--- a/ROUTE_2_PATH2_ADMIN_MBA_LIB_AIML_AUDI/PATH2_FINAL_ODK.xlsx
+++ b/ROUTE_2_PATH2_ADMIN_MBA_LIB_AIML_AUDI/PATH2_FINAL_ODK.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:J88"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,15 +418,18 @@
         <v>required</v>
       </c>
       <c r="F1" t="str">
+        <v>required_message</v>
+      </c>
+      <c r="G1" t="str">
         <v>constraint</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>constraint_message</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>relevant</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>media::image</v>
       </c>
     </row>
@@ -446,22 +449,47 @@
         <v>note</v>
       </c>
       <c r="B3" t="str">
-        <v>start_rules_note</v>
+        <v>instructions_rules_note</v>
       </c>
       <c r="C3" t="str" xml:space="preserve">
         <v xml:space="preserve">🏆 FINAL CLUE — PATH 2
-### 🏴 TREASURE HUNT — RULES
-1. *No phones allowed* during the hunt. Keep them switched off and safely stored.
-2. *Stay with your team* and follow the designated route/instructions.
-3. *No cheating or interference* with other teams, clues, props, or college property.
-4. Complete all challenges *as instructed by the coordinators*. Safety comes first.
-5. Any violation of the rules may result in a *time penalty or disqualification*. The coordinator’s decision will be final.
-⚠️ IMPORTANT:
-• All questions, code entries, and photo uploads are MANDATORY.
-• All text answers and codes must be entered in UPPERCASE ONLY.</v>
+TREASURE HUNT FOR FRESHERS 2026
+Welcome to PATH 2 of the Final Clue Treasure Hunt!
+Instructions:
+Rules and Regulations:
+* Participants must report to the designated starting point 5–10 minutes before the event begins.
+* Each team must consist of 3–4 members.
+* At least one member of the team should have an Android phone.
+* Each team will receive the first clue at the beginning of the event.
+* Teams must solve each clue to find the location of the next clue.
+* Clues must be solved in the given sequence.
+* Teams are not allowed to take, hide, damage, or tamper with clues belonging to other teams.
+* Teams must remain within the designated event area.
+* Running in unsafe areas or restricted zones is prohibited.
+* Participants must not enter restricted areas or disturb ongoing events/classes.
+* Physical force, pushing, blocking, or interfering with other teams is strictly prohibited.
+* Only one device containing ODK Collect is allowed per team.
+* No use of Wi-Fi unless specifically specified. Otherwise, the team may be disqualified.
+* Participants must not damage or move any property while searching for clues.
+* Teams must follow instructions given by volunteers and organizers at all times.
+* Asking people outside the team for answers or assistance is not allowed.
+* Teams must not follow, copy, or deliberately interfere with another team's progress.
+* Tampering with clues, cheating, entering restricted areas, or intentionally misleading other teams may result in immediate disqualification.
+* The Organizing Committee will not be responsible for the loss or damage of any personal belongings of participants.
+🏆 TEAM QUALIFICATION RULES (PER PATH):
+There are 5 rounds in each path.
+From each path:
+* First 25 teams proceed to Round 2.
+* Next 15 teams proceed to Round 3.
+* Next 7 teams proceed to Round 4.
+* Next 2 teams proceed to Round 5.
+⚠️ MANDATORY RESPONSE &amp; CAPS ONLY RULES:
+• Every single question, photo upload, and code entry is strictly MANDATORY.
+• All text answers and volunteer codes must be entered in UPPERCASE (CAPS ONLY).
+• Lowercase letters will be rejected by validation.</v>
       </c>
       <c r="D3" t="str">
-        <v>Read all rules carefully before proceeding.</v>
+        <v>Read all rules and instructions carefully.</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -472,7 +500,7 @@
         <v>team_name</v>
       </c>
       <c r="C4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Team Name
+        <v xml:space="preserve">Enter Team Name (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D4" t="str">
@@ -482,9 +510,12 @@
         <v>yes</v>
       </c>
       <c r="F4" t="str">
+        <v>❌ Team Name is mandatory. Please enter in UPPERCASE.</v>
+      </c>
+      <c r="G4" t="str">
         <v>regex(., '^[A-Z0-9\-_ ]+$')</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>❌ Please enter Team Name in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
@@ -496,7 +527,7 @@
         <v>player_id</v>
       </c>
       <c r="C5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Team / Player Identification
+        <v xml:space="preserve">Enter Team / Player Identification (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D5" t="str">
@@ -506,9 +537,12 @@
         <v>yes</v>
       </c>
       <c r="F5" t="str">
+        <v>❌ Player / Team ID is mandatory. Please enter in UPPERCASE.</v>
+      </c>
+      <c r="G5" t="str">
         <v>regex(., '^[A-Z0-9\-_ ]+$')</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>❌ Please enter Player/Team Identification in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
@@ -520,7 +554,7 @@
         <v>team_start_photo</v>
       </c>
       <c r="C6" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Team Verification Photo
+        <v xml:space="preserve">📸 Upload Team Verification Photo (MANDATORY)
 Photo upload is mandatory</v>
       </c>
       <c r="D6" t="str">
@@ -528,6 +562,9 @@
       </c>
       <c r="E6" t="str">
         <v>yes</v>
+      </c>
+      <c r="F6" t="str">
+        <v>❌ Team verification photo is strictly mandatory.</v>
       </c>
     </row>
     <row r="7">
@@ -545,7 +582,7 @@
       <c r="C8" t="str">
         <v>ROUND 1 — OBJECT FINDING</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != ''</v>
       </c>
     </row>
@@ -557,16 +594,16 @@
         <v>r1_admin_note</v>
       </c>
       <c r="C9" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 1: 🧩 OBJECT FINDING
-Challenge: Search the location to find the assigned hidden object/code.
+        <v xml:space="preserve">📍 ROUND 1: OBJECT FINDING
 Instructions:
-1. Search the location to find the assigned hidden object.
-2. Take a clear photo of the object.
-3. Show the photo to the station volunteer to receive your verification code.
+1. Find the assigned object.
+2. Take a mandatory photo of the object.
+3. Show the object/photo to a nearby Luminus ID-card volunteer.
+4. Enter the Round 1 completion code given by the volunteer.
 Enter code in caps</v>
       </c>
       <c r="D9" t="str">
-        <v>Find the assigned hidden object.</v>
+        <v>Find the assigned object, take photo, and ask volunteer for code.</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -577,7 +614,7 @@
         <v>r1_admin_photo</v>
       </c>
       <c r="C10" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of the Discovered Hidden Object
+        <v xml:space="preserve">📸 Upload Photo of the Discovered Hidden Object (MANDATORY)
 Photo upload is mandatory</v>
       </c>
       <c r="D10" t="str">
@@ -586,6 +623,9 @@
       <c r="E10" t="str">
         <v>yes</v>
       </c>
+      <c r="F10" t="str">
+        <v>❌ Photo upload of the object is mandatory.</v>
+      </c>
     </row>
     <row r="11" xml:space="preserve">
       <c r="A11" t="str">
@@ -595,7 +635,7 @@
         <v>r1_admin_code</v>
       </c>
       <c r="C11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Verification Code
+        <v xml:space="preserve">Enter Volunteer Verification Code (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D11" t="str">
@@ -605,10 +645,13 @@
         <v>yes</v>
       </c>
       <c r="F11" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JOHN-CENA'</v>
+        <v>❌ Volunteer verification code is mandatory.</v>
       </c>
       <c r="G11" t="str">
-        <v>❌ Incorrect code. Enter the code in CAPS provided by the volunteer.</v>
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'JOHN-CENA'</v>
+      </c>
+      <c r="H11" t="str">
+        <v>❌ Incorrect code. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
       </c>
     </row>
     <row r="12">
@@ -626,8 +669,8 @@
       <c r="C13" t="str">
         <v>ROUND 2 LOCATION CLUE</v>
       </c>
-      <c r="H13" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_admin_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JOHN-CENA' and ${r1_admin_photo} != ''</v>
+      <c r="I13" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != ''</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
@@ -638,15 +681,12 @@
         <v>r2_mba_loc_note</v>
       </c>
       <c r="C14" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 2 LOCATION CLUE
-One neighbour has already chosen its path.
-The other is still preparing for the journey ahead.
-Between the experienced and the yet-to-begin,
-your next destination quietly stands.
+        <v xml:space="preserve">At 14:30, the security team detected an unusual login attempt on the college network. The account was accessed from an unknown device shortly after the user received a suspicious email. The security team immediately changed the account credentmials and checked the systbem logs for unusual activity. No confidential files appeared to have been downloaded during the incident. The affected user was advised to enable multi-factor authentication and avoid opening links from unknown senders. The incident was then reported to the network administrataor for further investigation.The report has been tampered with. The intruder left three traces behind.
+Find the words that don't belong and recover what was hidden: credentials → credentmials, system → systbem ,administrator → administrataor The inserted letters are:
 Enter code in caps</v>
       </c>
       <c r="D14" t="str">
-        <v>Read the riddle to deduce the destination block.</v>
+        <v>Deduce the inserted letters and enter the destination.</v>
       </c>
     </row>
     <row r="15" xml:space="preserve">
@@ -657,7 +697,7 @@
         <v>r2_mba_loc_answer</v>
       </c>
       <c r="C15" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter destination location
+        <v xml:space="preserve">Enter destination location (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D15" t="str">
@@ -667,47 +707,66 @@
         <v>yes</v>
       </c>
       <c r="F15" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK'</v>
+        <v>❌ Destination location is mandatory.</v>
       </c>
       <c r="G15" t="str">
-        <v>❌ Incorrect destination. Read the clue carefully and enter in CAPS.</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'MBA' or normalize-space(.) = 'MBA BLOCK')</v>
+      </c>
+      <c r="H15" t="str">
+        <v>❌ Incorrect destination. Read the clue carefully and enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
       <c r="A16" t="str">
+        <v>note</v>
+      </c>
+      <c r="B16" t="str">
+        <v>r2_proceed_note</v>
+      </c>
+      <c r="C16" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏃 Go to the location you identified and ask the Luminus volunteer there for the START CODE.
+Enter code in caps</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Go to the location and ask volunteer for start code.</v>
+      </c>
+      <c r="I16" t="str">
+        <v>normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK'</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>text</v>
+      </c>
+      <c r="B17" t="str">
+        <v>r2_start_code</v>
+      </c>
+      <c r="C17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter START CODE from Volunteer (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D17" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E17" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F17" t="str">
+        <v>❌ START CODE is mandatory.</v>
+      </c>
+      <c r="G17" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'MBA-START'</v>
+      </c>
+      <c r="H17" t="str">
+        <v>❌ Incorrect START CODE. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
+      </c>
+      <c r="I17" t="str">
+        <v>normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK'</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>end_group</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>begin_group</v>
-      </c>
-      <c r="B17" t="str">
-        <v>mba_challenge_group</v>
-      </c>
-      <c r="C17" t="str">
-        <v>ROUND 2 — MINI CHALLENGE</v>
-      </c>
-      <c r="H17" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_admin_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JOHN-CENA' and ${r1_admin_photo} != '' and (translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK')</v>
-      </c>
-    </row>
-    <row r="18" xml:space="preserve">
-      <c r="A18" t="str">
-        <v>select_one mba_variants</v>
-      </c>
-      <c r="B18" t="str">
-        <v>mba_variant_select</v>
-      </c>
-      <c r="C18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Select Assigned Challenge Variant
-Mandatory selection</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Select the variant set assigned by the station volunteer.</v>
-      </c>
-      <c r="E18" t="str">
-        <v>yes</v>
       </c>
     </row>
     <row r="19">
@@ -715,77 +774,64 @@
         <v>begin_group</v>
       </c>
       <c r="B19" t="str">
-        <v>mba_v1_group</v>
+        <v>mba_challenge_group</v>
       </c>
       <c r="C19" t="str">
-        <v>VARIANT 1 — MBA QUICKFIRE (SET A)</v>
-      </c>
-      <c r="H19" t="str">
-        <v>${mba_variant_select} = 'mba_01'</v>
+        <v>ROUND 2 — MINI CHALLENGE</v>
+      </c>
+      <c r="I19" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START'</v>
       </c>
     </row>
     <row r="20" xml:space="preserve">
       <c r="A20" t="str">
-        <v>note</v>
+        <v>select_one mba_variants</v>
       </c>
       <c r="B20" t="str">
-        <v>mba_v1_intro</v>
+        <v>mba_variant_select</v>
       </c>
       <c r="C20" t="str" xml:space="preserve">
-        <v xml:space="preserve">📊 MINI-CHALLENGE: MBA QUICKFIRE (SET A)
-Answer all 10 quickfire business &amp; management questions below.
-Enter code in caps</v>
+        <v xml:space="preserve">Select your assigned challenge variant: (MANDATORY)
+Mandatory selection</v>
       </c>
       <c r="D20" t="str">
-        <v>Answer all 10 questions in CAPS.</v>
-      </c>
-    </row>
-    <row r="21" xml:space="preserve">
+        <v>Choose Variant A or Variant B as assigned by the volunteer.</v>
+      </c>
+      <c r="E20" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F20" t="str">
+        <v>❌ Selecting your assigned variant is mandatory.</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="str">
-        <v>text</v>
+        <v>begin_group</v>
       </c>
       <c r="B21" t="str">
-        <v>mba_q1</v>
-      </c>
-      <c r="C21" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. A market with only one seller is called?
-Enter code in caps</v>
-      </c>
-      <c r="D21" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E21" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F21" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONOPOLY'</v>
-      </c>
-      <c r="G21" t="str">
-        <v>❌ Incorrect answer. Please enter in CAPS.</v>
+        <v>mba_v1_group</v>
+      </c>
+      <c r="C21" t="str">
+        <v>VARIANT A</v>
+      </c>
+      <c r="I21" t="str">
+        <v>${mba_variant_select} = 'var_a'</v>
       </c>
     </row>
     <row r="22" xml:space="preserve">
       <c r="A22" t="str">
-        <v>text</v>
+        <v>note</v>
       </c>
       <c r="B22" t="str">
-        <v>mba_q2</v>
+        <v>mba_v1_intro</v>
       </c>
       <c r="C22" t="str" xml:space="preserve">
-        <v xml:space="preserve">2. What is the currency of China?
+        <v xml:space="preserve">📊 VARIANT A: MBA QUICKFIRE
+Answer all 10 quickfire questions below.
 Enter code in caps</v>
       </c>
       <c r="D22" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E22" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F22" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'YUAN'</v>
-      </c>
-      <c r="G22" t="str">
-        <v>❌ Incorrect answer. Please enter in CAPS.</v>
+        <v>Answer all 10 questions in CAPS.</v>
       </c>
     </row>
     <row r="23" xml:space="preserve">
@@ -793,10 +839,10 @@
         <v>text</v>
       </c>
       <c r="B23" t="str">
-        <v>mba_q3</v>
+        <v>mba_q1</v>
       </c>
       <c r="C23" t="str" xml:space="preserve">
-        <v xml:space="preserve">3. What does CEO stand for?
+        <v xml:space="preserve">1. A market with only one seller is called? (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D23" t="str">
@@ -806,10 +852,13 @@
         <v>yes</v>
       </c>
       <c r="F23" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CHIEF EXECUTIVE OFFICER'</v>
+        <v>❌ Question 1 is mandatory.</v>
       </c>
       <c r="G23" t="str">
-        <v>❌ Incorrect answer. Please enter in CAPS.</v>
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'MONOPOLY'</v>
+      </c>
+      <c r="H23" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="24" xml:space="preserve">
@@ -817,10 +866,10 @@
         <v>text</v>
       </c>
       <c r="B24" t="str">
-        <v>mba_q4</v>
+        <v>mba_q2</v>
       </c>
       <c r="C24" t="str" xml:space="preserve">
-        <v xml:space="preserve">4. What does ROI stand for in business finance?
+        <v xml:space="preserve">2. What is the currency of China? (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D24" t="str">
@@ -830,10 +879,13 @@
         <v>yes</v>
       </c>
       <c r="F24" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RETURN ON INVESTMENT'</v>
+        <v>❌ Question 2 is mandatory.</v>
       </c>
       <c r="G24" t="str">
-        <v>❌ Incorrect answer. Please enter in CAPS.</v>
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'YUAN'</v>
+      </c>
+      <c r="H24" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="25" xml:space="preserve">
@@ -841,10 +893,10 @@
         <v>text</v>
       </c>
       <c r="B25" t="str">
-        <v>mba_q5</v>
+        <v>mba_q3</v>
       </c>
       <c r="C25" t="str" xml:space="preserve">
-        <v xml:space="preserve">5. What term describes business transactions conducted between two companies (abbreviation)?
+        <v xml:space="preserve">3. What does CEO stand for? (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D25" t="str">
@@ -854,10 +906,13 @@
         <v>yes</v>
       </c>
       <c r="F25" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'B2B'</v>
+        <v>❌ Question 3 is mandatory.</v>
       </c>
       <c r="G25" t="str">
-        <v>❌ Incorrect answer. Please enter in CAPS.</v>
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'CHIEF EXECUTIVE OFFICER'</v>
+      </c>
+      <c r="H25" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="26" xml:space="preserve">
@@ -865,10 +920,10 @@
         <v>text</v>
       </c>
       <c r="B26" t="str">
-        <v>mba_q6</v>
+        <v>mba_q4</v>
       </c>
       <c r="C26" t="str" xml:space="preserve">
-        <v xml:space="preserve">6. In accounting: Assets minus Liabilities equals what?
+        <v xml:space="preserve">4. What does ROI stand for in business finance? (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D26" t="str">
@@ -878,10 +933,13 @@
         <v>yes</v>
       </c>
       <c r="F26" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'EQUITY'</v>
+        <v>❌ Question 4 is mandatory.</v>
       </c>
       <c r="G26" t="str">
-        <v>❌ Incorrect answer. Please enter in CAPS.</v>
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'RETURN ON INVESTMENT'</v>
+      </c>
+      <c r="H26" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="27" xml:space="preserve">
@@ -889,10 +947,10 @@
         <v>text</v>
       </c>
       <c r="B27" t="str">
-        <v>mba_q7</v>
+        <v>mba_q5</v>
       </c>
       <c r="C27" t="str" xml:space="preserve">
-        <v xml:space="preserve">7. Which animal represents a rising, optimistic financial market?
+        <v xml:space="preserve">5. What term describes business transactions conducted between two companies (abbreviation)? (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D27" t="str">
@@ -902,10 +960,13 @@
         <v>yes</v>
       </c>
       <c r="F27" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BULL'</v>
+        <v>❌ Question 5 is mandatory.</v>
       </c>
       <c r="G27" t="str">
-        <v>❌ Incorrect answer. Please enter in CAPS.</v>
+        <v>regex(., '^[A-Z0-9]+$') and normalize-space(.) = 'B2B'</v>
+      </c>
+      <c r="H27" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="28" xml:space="preserve">
@@ -913,10 +974,10 @@
         <v>text</v>
       </c>
       <c r="B28" t="str">
-        <v>mba_q8</v>
+        <v>mba_q6</v>
       </c>
       <c r="C28" t="str" xml:space="preserve">
-        <v xml:space="preserve">8. What does IPO stand for when a company goes public?
+        <v xml:space="preserve">6. In accounting: Assets minus Liabilities equals what? (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D28" t="str">
@@ -926,10 +987,13 @@
         <v>yes</v>
       </c>
       <c r="F28" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'INITIAL PUBLIC OFFERING'</v>
+        <v>❌ Question 6 is mandatory.</v>
       </c>
       <c r="G28" t="str">
-        <v>❌ Incorrect answer. Please enter in CAPS.</v>
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'EQUITY'</v>
+      </c>
+      <c r="H28" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
@@ -937,10 +1001,10 @@
         <v>text</v>
       </c>
       <c r="B29" t="str">
-        <v>mba_q9</v>
+        <v>mba_q7</v>
       </c>
       <c r="C29" t="str" xml:space="preserve">
-        <v xml:space="preserve">9. What is the standard 3-letter abbreviation for Gross Domestic Product?
+        <v xml:space="preserve">7. Which animal represents a rising, optimistic financial market? (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D29" t="str">
@@ -950,10 +1014,13 @@
         <v>yes</v>
       </c>
       <c r="F29" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GDP'</v>
+        <v>❌ Question 7 is mandatory.</v>
       </c>
       <c r="G29" t="str">
-        <v>❌ Incorrect answer. Please enter in CAPS.</v>
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'BULL'</v>
+      </c>
+      <c r="H29" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="30" xml:space="preserve">
@@ -961,10 +1028,10 @@
         <v>text</v>
       </c>
       <c r="B30" t="str">
-        <v>mba_q10</v>
+        <v>mba_q8</v>
       </c>
       <c r="C30" t="str" xml:space="preserve">
-        <v xml:space="preserve">10. In the 4 Ps of Marketing (Product, Price, Place), what is the 4th P?
+        <v xml:space="preserve">8. What does IPO stand for when a company goes public? (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D30" t="str">
@@ -974,86 +1041,132 @@
         <v>yes</v>
       </c>
       <c r="F30" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PROMOTION'</v>
+        <v>❌ Question 8 is mandatory.</v>
       </c>
       <c r="G30" t="str">
-        <v>❌ Incorrect answer. Please enter in CAPS.</v>
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'INITIAL PUBLIC OFFERING'</v>
+      </c>
+      <c r="H30" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="31" xml:space="preserve">
       <c r="A31" t="str">
-        <v>image</v>
+        <v>text</v>
       </c>
       <c r="B31" t="str">
-        <v>r2_var1_quickfire_photo</v>
+        <v>mba_q9</v>
       </c>
       <c r="C31" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Team Completing Quickfire Challenge
-Photo upload is mandatory</v>
+        <v xml:space="preserve">9. What is the standard 3-letter abbreviation for Gross Domestic Product? (MANDATORY)
+Enter code in caps</v>
       </c>
       <c r="D31" t="str">
-        <v>Take a clear photo of your team at the station.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
       </c>
       <c r="E31" t="str">
         <v>yes</v>
       </c>
-    </row>
-    <row r="32">
+      <c r="F31" t="str">
+        <v>❌ Question 9 is mandatory.</v>
+      </c>
+      <c r="G31" t="str">
+        <v>regex(., '^[A-Z]+$') and normalize-space(.) = 'GDP'</v>
+      </c>
+      <c r="H31" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
       <c r="A32" t="str">
+        <v>text</v>
+      </c>
+      <c r="B32" t="str">
+        <v>mba_q10</v>
+      </c>
+      <c r="C32" t="str" xml:space="preserve">
+        <v xml:space="preserve">10. In the 4 Ps of Marketing (Product, Price, Place), what is the 4th P? (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D32" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E32" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F32" t="str">
+        <v>❌ Question 10 is mandatory.</v>
+      </c>
+      <c r="G32" t="str">
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'PROMOTION'</v>
+      </c>
+      <c r="H32" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
+        <v>text</v>
+      </c>
+      <c r="B33" t="str">
+        <v>r2_var_a_code</v>
+      </c>
+      <c r="C33" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Completion Code from Volunteer (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D33" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E33" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F33" t="str">
+        <v>❌ Completion code is mandatory.</v>
+      </c>
+      <c r="G33" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'MBA-QF-1'</v>
+      </c>
+      <c r="H33" t="str">
+        <v>❌ Incorrect completion code. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
+      </c>
+      <c r="I33" t="str">
+        <v>(normalize-space(${mba_q1}) = 'MONOPOLY' and normalize-space(${mba_q2}) = 'YUAN' and normalize-space(${mba_q3}) = 'CHIEF EXECUTIVE OFFICER' and normalize-space(${mba_q4}) = 'RETURN ON INVESTMENT' and normalize-space(${mba_q5}) = 'B2B' and normalize-space(${mba_q6}) = 'EQUITY' and normalize-space(${mba_q7}) = 'BULL' and normalize-space(${mba_q8}) = 'INITIAL PUBLIC OFFERING' and normalize-space(${mba_q9}) = 'GDP' and normalize-space(${mba_q10}) = 'PROMOTION')</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
         <v>end_group</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="str">
+    <row r="35">
+      <c r="A35" t="str">
         <v>begin_group</v>
       </c>
-      <c r="B33" t="str">
+      <c r="B35" t="str">
         <v>mba_v2_group</v>
       </c>
-      <c r="C33" t="str">
-        <v>VARIANT 2 — MBA QUICKFIRE (SET B)</v>
-      </c>
-      <c r="H33" t="str">
-        <v>${mba_variant_select} = 'mba_02'</v>
-      </c>
-    </row>
-    <row r="34" xml:space="preserve">
-      <c r="A34" t="str">
+      <c r="C35" t="str">
+        <v>VARIANT B</v>
+      </c>
+      <c r="I35" t="str">
+        <v>${mba_variant_select} = 'var_b'</v>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
         <v>note</v>
       </c>
-      <c r="B34" t="str">
-        <v>mba_v2_placeholder</v>
-      </c>
-      <c r="C34" t="str" xml:space="preserve">
-        <v xml:space="preserve">BRAND QUIZ / QUICKFIRE SET B CONTENT TO BE ADDED
-Participants solve the assigned Variant 2 questions.
-[CONTENT TO BE ADDED BY ORGANIZER BEFORE DEPLOYMENT]</v>
-      </c>
-      <c r="D34" t="str">
-        <v>Organizer placeholder — to be updated before deployment.</v>
-      </c>
-    </row>
-    <row r="35" xml:space="preserve">
-      <c r="A35" t="str">
-        <v>image</v>
-      </c>
-      <c r="B35" t="str">
-        <v>r2_var2_quickfire_photo</v>
-      </c>
-      <c r="C35" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Team Completing Variant 2 Challenge
-Photo upload is mandatory</v>
-      </c>
-      <c r="D35" t="str">
-        <v>Take a clear photo of your team at the station.</v>
-      </c>
-      <c r="E35" t="str">
-        <v>yes</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>end_group</v>
+      <c r="B36" t="str">
+        <v>mba_v2_intro</v>
+      </c>
+      <c r="C36" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏷️ VARIANT B: BRAND QUIZ
+Answer all 10 brand quiz questions below.
+Enter code in caps</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Answer all 10 brand questions in CAPS.</v>
       </c>
     </row>
     <row r="37" xml:space="preserve">
@@ -1061,10 +1174,10 @@
         <v>text</v>
       </c>
       <c r="B37" t="str">
-        <v>r2_mba_clearance_code</v>
+        <v>r2_b_q1</v>
       </c>
       <c r="C37" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Clearance Code
+        <v xml:space="preserve">1. Name of dessert? (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D37" t="str">
@@ -1074,52 +1187,103 @@
         <v>yes</v>
       </c>
       <c r="F37" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA-QF-1'</v>
+        <v>❌ Question 1 is mandatory.</v>
       </c>
       <c r="G37" t="str">
-        <v>❌ Incorrect clearance code. Obtain clearance code in CAPS from the MBA volunteer.</v>
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'BAMBALONI'</v>
       </c>
       <c r="H37" t="str">
-        <v>(((translate(normalize-space(${mba_q1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONOPOLY' and translate(normalize-space(${mba_q2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'YUAN' and translate(normalize-space(${mba_q3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CHIEF EXECUTIVE OFFICER' and translate(normalize-space(${mba_q4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RETURN ON INVESTMENT' and translate(normalize-space(${mba_q5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'B2B' and translate(normalize-space(${mba_q6}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'EQUITY' and translate(normalize-space(${mba_q7}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BULL' and translate(normalize-space(${mba_q8}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'INITIAL PUBLIC OFFERING' and translate(normalize-space(${mba_q9}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GDP' and translate(normalize-space(${mba_q10}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PROMOTION' and ${r2_var1_quickfire_photo} != '') and ${mba_variant_select} = 'mba_01') or (${mba_variant_select} = 'mba_02' and ${r2_var2_quickfire_photo} != ''))</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="J37" t="str">
+        <v>bambaloni.jpeg</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
       <c r="A38" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>text</v>
+      </c>
+      <c r="B38" t="str">
+        <v>r2_b_q2</v>
+      </c>
+      <c r="C38" t="str" xml:space="preserve">
+        <v xml:space="preserve">2. Which brand is associated with this tagline? “THINK DIFFERENT” (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D38" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E38" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F38" t="str">
+        <v>❌ Question 2 is mandatory.</v>
+      </c>
+      <c r="G38" t="str">
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'APPLE'</v>
+      </c>
+      <c r="H38" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
       <c r="A39" t="str">
-        <v>begin_group</v>
+        <v>text</v>
       </c>
       <c r="B39" t="str">
-        <v>r3_lib_loc_group</v>
-      </c>
-      <c r="C39" t="str">
-        <v>ROUND 3 LOCATION CLUE</v>
+        <v>r2_b_q3</v>
+      </c>
+      <c r="C39" t="str" xml:space="preserve">
+        <v xml:space="preserve">3. What is the name of the cartoon this character represents? (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D39" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E39" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F39" t="str">
+        <v>❌ Question 3 is mandatory.</v>
+      </c>
+      <c r="G39" t="str">
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'HORRID HENRY'</v>
       </c>
       <c r="H39" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_admin_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JOHN-CENA' and ${r1_admin_photo} != '' and (translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK') and (((translate(normalize-space(${mba_q1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONOPOLY' and translate(normalize-space(${mba_q2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'YUAN' and translate(normalize-space(${mba_q3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CHIEF EXECUTIVE OFFICER' and translate(normalize-space(${mba_q4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RETURN ON INVESTMENT' and translate(normalize-space(${mba_q5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'B2B' and translate(normalize-space(${mba_q6}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'EQUITY' and translate(normalize-space(${mba_q7}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BULL' and translate(normalize-space(${mba_q8}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'INITIAL PUBLIC OFFERING' and translate(normalize-space(${mba_q9}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GDP' and translate(normalize-space(${mba_q10}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PROMOTION' and ${r2_var1_quickfire_photo} != '') and ${mba_variant_select} = 'mba_01') or (${mba_variant_select} = 'mba_02' and ${r2_var2_quickfire_photo} != '')) and translate(normalize-space(${r2_mba_clearance_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA-QF-1'</v>
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="J39" t="str">
+        <v>horrid henry.jpeg</v>
       </c>
     </row>
     <row r="40" xml:space="preserve">
       <c r="A40" t="str">
-        <v>note</v>
+        <v>text</v>
       </c>
       <c r="B40" t="str">
-        <v>r3_lib_loc_note</v>
+        <v>r2_b_q4</v>
       </c>
       <c r="C40" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 3 LOCATION CLUE
-VEHSELS
-GIDRAEN
-IFIW
-SISCUDISNO GGUONLE
-IGIDLAT BILRYRA
+        <v xml:space="preserve">4. Identify the brand from this famous ad screenshot. (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D40" t="str">
-        <v>Decode the anagrams to identify the next destination.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E40" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F40" t="str">
+        <v>❌ Question 4 is mandatory.</v>
+      </c>
+      <c r="G40" t="str">
+        <v>regex(., '^[A-Z0-9 ]+$') and (normalize-space(.) = '5 STAR' or normalize-space(.) = '5STAR' or normalize-space(.) = 'FIVE STAR')</v>
+      </c>
+      <c r="H40" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="J40" t="str">
+        <v>5 star.jpeg</v>
       </c>
     </row>
     <row r="41" xml:space="preserve">
@@ -1127,10 +1291,10 @@
         <v>text</v>
       </c>
       <c r="B41" t="str">
-        <v>r3_lib_loc_answer</v>
+        <v>r2_b_q5</v>
       </c>
       <c r="C41" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter confirmed destination location
+        <v xml:space="preserve">5. Can you identify the brand from this zoomed-in logo? (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D41" t="str">
@@ -1140,57 +1304,115 @@
         <v>yes</v>
       </c>
       <c r="F41" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY'</v>
+        <v>❌ Question 5 is mandatory.</v>
       </c>
       <c r="G41" t="str">
-        <v>❌ Incorrect destination. Decode the anagrams to identify the location in CAPS.</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'NOKIA'</v>
+      </c>
+      <c r="H41" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="J41" t="str">
+        <v>nokia.jpeg</v>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
       <c r="A42" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>text</v>
+      </c>
+      <c r="B42" t="str">
+        <v>r2_b_q6</v>
+      </c>
+      <c r="C42" t="str" xml:space="preserve">
+        <v xml:space="preserve">6. What is the name of this fruit? (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D42" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E42" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F42" t="str">
+        <v>❌ Question 6 is mandatory.</v>
+      </c>
+      <c r="G42" t="str">
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'DURIAN'</v>
+      </c>
+      <c r="H42" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="J42" t="str">
+        <v>durian.jpeg</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
       <c r="A43" t="str">
-        <v>begin_group</v>
+        <v>text</v>
       </c>
       <c r="B43" t="str">
-        <v>r3_lib_qr_group</v>
-      </c>
-      <c r="C43" t="str">
-        <v>ROUND 3 — QR HUNT</v>
+        <v>r2_b_q7</v>
+      </c>
+      <c r="C43" t="str" xml:space="preserve">
+        <v xml:space="preserve">7. Which brand is associated with this tagline? “WHEREVER YOU GO, OUR NETWORK FOLLOWS” (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D43" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E43" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F43" t="str">
+        <v>❌ Question 7 is mandatory.</v>
+      </c>
+      <c r="G43" t="str">
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'VODAFONE'</v>
       </c>
       <c r="H43" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_admin_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JOHN-CENA' and ${r1_admin_photo} != '' and (translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK') and (((translate(normalize-space(${mba_q1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONOPOLY' and translate(normalize-space(${mba_q2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'YUAN' and translate(normalize-space(${mba_q3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CHIEF EXECUTIVE OFFICER' and translate(normalize-space(${mba_q4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RETURN ON INVESTMENT' and translate(normalize-space(${mba_q5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'B2B' and translate(normalize-space(${mba_q6}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'EQUITY' and translate(normalize-space(${mba_q7}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BULL' and translate(normalize-space(${mba_q8}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'INITIAL PUBLIC OFFERING' and translate(normalize-space(${mba_q9}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GDP' and translate(normalize-space(${mba_q10}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PROMOTION' and ${r2_var1_quickfire_photo} != '') and ${mba_variant_select} = 'mba_01') or (${mba_variant_select} = 'mba_02' and ${r2_var2_quickfire_photo} != '')) and translate(normalize-space(${r2_mba_clearance_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA-QF-1' and (translate(normalize-space(${r3_lib_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(${r3_lib_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY')</v>
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="44" xml:space="preserve">
       <c r="A44" t="str">
-        <v>note</v>
+        <v>text</v>
       </c>
       <c r="B44" t="str">
-        <v>r3_lib_qr_note</v>
+        <v>r2_b_q8</v>
       </c>
       <c r="C44" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 3: QR HUNT
-Search the location physically to locate the hidden QR code.
-Scan the QR code using the scanner below.
+        <v xml:space="preserve">8. Which brand does this mascot represent? (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D44" t="str">
-        <v>Locate and scan the hidden QR code.</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E44" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F44" t="str">
+        <v>❌ Question 8 is mandatory.</v>
+      </c>
+      <c r="G44" t="str">
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'MICHELIN'</v>
+      </c>
+      <c r="H44" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="J44" t="str">
+        <v>michelin.jpeg</v>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
       <c r="A45" t="str">
-        <v>barcode</v>
+        <v>text</v>
       </c>
       <c r="B45" t="str">
-        <v>r3_lib_qr_scan</v>
-      </c>
-      <c r="C45" t="str">
-        <v>Scan Discovered QR Code</v>
+        <v>r2_b_q9</v>
+      </c>
+      <c r="C45" t="str" xml:space="preserve">
+        <v xml:space="preserve">9. What is the full name of RN Shetty? (MANDATORY)
+Enter code in caps</v>
       </c>
       <c r="D45" t="str">
         <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
@@ -1199,125 +1421,114 @@
         <v>yes</v>
       </c>
       <c r="F45" t="str">
-        <v>normalize-space(.) = 'DUMB_FAKE' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DUMB_FAKE'</v>
+        <v>❌ Question 9 is mandatory.</v>
       </c>
       <c r="G45" t="str">
-        <v>❌ Incorrect QR code scanned. Search for the correct QR code at this station.</v>
+        <v>regex(., '^[A-Z0-9\.\- ]+$') and (normalize-space(.) = 'DR. RAMA NAGAPPA SHETTY' or normalize-space(.) = 'RAMA NAGAPPA SHETTY' or normalize-space(.) = 'DR RAMA NAGAPPA SHETTY')</v>
+      </c>
+      <c r="H45" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="46" xml:space="preserve">
       <c r="A46" t="str">
-        <v>image</v>
+        <v>text</v>
       </c>
       <c r="B46" t="str">
-        <v>r3_lib_qr_photo</v>
+        <v>r2_b_q10</v>
       </c>
       <c r="C46" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Discovered QR Code / Station
-Photo upload is mandatory</v>
+        <v xml:space="preserve">10. This actress holds a brand of herself. What is the brand name? (MANDATORY)
+Enter code in caps</v>
       </c>
       <c r="D46" t="str">
-        <v>Take a clear photo of the discovered QR code location.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
       </c>
       <c r="E46" t="str">
         <v>yes</v>
       </c>
-    </row>
-    <row r="47">
+      <c r="F46" t="str">
+        <v>❌ Question 10 is mandatory.</v>
+      </c>
+      <c r="G46" t="str">
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'PALMONAS'</v>
+      </c>
+      <c r="H46" t="str">
+        <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="J46" t="str">
+        <v>palmonas.jpeg</v>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
       <c r="A47" t="str">
-        <v>end_group</v>
+        <v>text</v>
+      </c>
+      <c r="B47" t="str">
+        <v>r2_var_b_code</v>
+      </c>
+      <c r="C47" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Completion Code from Volunteer (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D47" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E47" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F47" t="str">
+        <v>❌ Completion code is mandatory.</v>
+      </c>
+      <c r="G47" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'MB-BQ-2'</v>
+      </c>
+      <c r="H47" t="str">
+        <v>❌ Incorrect completion code. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
+      </c>
+      <c r="I47" t="str">
+        <v>(normalize-space(${r2_b_q1}) = 'BAMBALONI' and normalize-space(${r2_b_q2}) = 'APPLE' and normalize-space(${r2_b_q3}) = 'HORRID HENRY' and (normalize-space(${r2_b_q4}) = '5 STAR' or normalize-space(${r2_b_q4}) = '5STAR' or normalize-space(${r2_b_q4}) = 'FIVE STAR') and normalize-space(${r2_b_q5}) = 'NOKIA' and normalize-space(${r2_b_q6}) = 'DURIAN' and normalize-space(${r2_b_q7}) = 'VODAFONE' and normalize-space(${r2_b_q8}) = 'MICHELIN' and (normalize-space(${r2_b_q9}) = 'DR. RAMA NAGAPPA SHETTY' or normalize-space(${r2_b_q9}) = 'RAMA NAGAPPA SHETTY' or normalize-space(${r2_b_q9}) = 'DR RAMA NAGAPPA SHETTY') and normalize-space(${r2_b_q10}) = 'PALMONAS')</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
         <v>begin_group</v>
       </c>
-      <c r="B48" t="str">
-        <v>r4_wordsearch_group</v>
-      </c>
-      <c r="C48" t="str">
-        <v>ROUND 4 LOCATION CLUE: WORD SEARCH</v>
-      </c>
-      <c r="H48" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_admin_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JOHN-CENA' and ${r1_admin_photo} != '' and (translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK') and (((translate(normalize-space(${mba_q1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONOPOLY' and translate(normalize-space(${mba_q2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'YUAN' and translate(normalize-space(${mba_q3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CHIEF EXECUTIVE OFFICER' and translate(normalize-space(${mba_q4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RETURN ON INVESTMENT' and translate(normalize-space(${mba_q5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'B2B' and translate(normalize-space(${mba_q6}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'EQUITY' and translate(normalize-space(${mba_q7}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BULL' and translate(normalize-space(${mba_q8}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'INITIAL PUBLIC OFFERING' and translate(normalize-space(${mba_q9}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GDP' and translate(normalize-space(${mba_q10}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PROMOTION' and ${r2_var1_quickfire_photo} != '') and ${mba_variant_select} = 'mba_01') or (${mba_variant_select} = 'mba_02' and ${r2_var2_quickfire_photo} != '')) and translate(normalize-space(${r2_mba_clearance_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA-QF-1' and (translate(normalize-space(${r3_lib_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(${r3_lib_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY') and (normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' or translate(normalize-space(${r3_lib_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DUMB_FAKE') and ${r3_lib_qr_photo} != ''</v>
-      </c>
-    </row>
-    <row r="49" xml:space="preserve">
-      <c r="A49" t="str">
-        <v>note</v>
-      </c>
-      <c r="B49" t="str">
-        <v>r4_wordsearch_intro</v>
-      </c>
-      <c r="C49" t="str" xml:space="preserve">
-        <v xml:space="preserve">🧩 ROUND 4 LOCATION CLUE: WORD SEARCH PUZZLE
-Examine the word search puzzle image below.
-Find and enter ANY 5 hidden technology concepts from the grid!
-Instructions:
-1. Spot at least 5 hidden words in the puzzle image.
-2. Enter each word in the fields below.
-3. After finding 5 valid words, deduce the destination campus block!
-Enter code in caps</v>
-      </c>
-      <c r="D49" t="str">
-        <v>Examine puzzle image and enter 5 discovered words in CAPS.</v>
-      </c>
-      <c r="I49" t="str">
-        <v>aiml.jpeg</v>
-      </c>
-    </row>
-    <row r="50" xml:space="preserve">
-      <c r="A50" t="str">
-        <v>text</v>
-      </c>
       <c r="B50" t="str">
-        <v>r4_ws_word1</v>
-      </c>
-      <c r="C50" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Discovered Word 1 (from puzzle image):
-Enter code in caps</v>
-      </c>
-      <c r="D50" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E50" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F50" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY'</v>
-      </c>
-      <c r="G50" t="str">
-        <v>❌ Invalid word. Enter a valid word found in the puzzle in CAPS.</v>
+        <v>r3_lib_loc_group</v>
+      </c>
+      <c r="C50" t="str">
+        <v>ROUND 3</v>
       </c>
       <c r="I50" t="str">
-        <v>aiml.jpeg</v>
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2'))</v>
       </c>
     </row>
     <row r="51" xml:space="preserve">
       <c r="A51" t="str">
-        <v>text</v>
+        <v>note</v>
       </c>
       <c r="B51" t="str">
-        <v>r4_ws_word2</v>
+        <v>r3_shuffled_intro_note</v>
       </c>
       <c r="C51" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Discovered Word 2 (from puzzle image):
+        <v xml:space="preserve">📍 ROUND 3
+Decode each of the shuffled words below.
+E.g., OOBK ➔ BOOK, APPRE ➔ PAPER
 Enter code in caps</v>
       </c>
       <c r="D51" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E51" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F51" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY' and translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') != translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ')</v>
-      </c>
-      <c r="G51" t="str">
-        <v>❌ Invalid or duplicate word. Enter a different valid word from the puzzle in CAPS.</v>
-      </c>
-      <c r="I51" t="str">
-        <v>aiml.jpeg</v>
+        <v>Decode each shuffled word.</v>
       </c>
     </row>
     <row r="52" xml:space="preserve">
@@ -1325,10 +1536,10 @@
         <v>text</v>
       </c>
       <c r="B52" t="str">
-        <v>r4_ws_word3</v>
+        <v>r3_decode_w1</v>
       </c>
       <c r="C52" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Discovered Word 3 (from puzzle image):
+        <v xml:space="preserve">Decode Shuffled Word 1: [ VEHSELS ] (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D52" t="str">
@@ -1338,13 +1549,13 @@
         <v>yes</v>
       </c>
       <c r="F52" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY' and translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') != translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') and translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') != translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ')</v>
+        <v>❌ Decoding Word 1 is mandatory.</v>
       </c>
       <c r="G52" t="str">
-        <v>❌ Invalid or duplicate word. Enter a different valid word from the puzzle in CAPS.</v>
-      </c>
-      <c r="I52" t="str">
-        <v>aiml.jpeg</v>
+        <v>regex(., '^[A-Z]+$') and normalize-space(.) = 'SHELVES'</v>
+      </c>
+      <c r="H52" t="str">
+        <v>❌ Incorrect decoded word. Enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="53" xml:space="preserve">
@@ -1352,10 +1563,10 @@
         <v>text</v>
       </c>
       <c r="B53" t="str">
-        <v>r4_ws_word4</v>
+        <v>r3_decode_w2</v>
       </c>
       <c r="C53" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Discovered Word 4 (from puzzle image):
+        <v xml:space="preserve">Decode Shuffled Word 2: [ GIDRAEN ] (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D53" t="str">
@@ -1365,13 +1576,13 @@
         <v>yes</v>
       </c>
       <c r="F53" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY' and translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') != translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') and translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') != translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') and translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') != translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ')</v>
+        <v>❌ Decoding Word 2 is mandatory.</v>
       </c>
       <c r="G53" t="str">
-        <v>❌ Invalid or duplicate word. Enter a different valid word from the puzzle in CAPS.</v>
-      </c>
-      <c r="I53" t="str">
-        <v>aiml.jpeg</v>
+        <v>regex(., '^[A-Z]+$') and normalize-space(.) = 'READING'</v>
+      </c>
+      <c r="H53" t="str">
+        <v>❌ Incorrect decoded word. Enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="54" xml:space="preserve">
@@ -1379,10 +1590,10 @@
         <v>text</v>
       </c>
       <c r="B54" t="str">
-        <v>r4_ws_word5</v>
+        <v>r3_decode_w3</v>
       </c>
       <c r="C54" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Discovered Word 5 (from puzzle image):
+        <v xml:space="preserve">Decode Shuffled Word 3: [ IFIW ] (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D54" t="str">
@@ -1392,13 +1603,13 @@
         <v>yes</v>
       </c>
       <c r="F54" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY' and translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') != translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') and translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') != translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') and translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') != translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') and translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') != translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ')</v>
+        <v>❌ Decoding Word 3 is mandatory.</v>
       </c>
       <c r="G54" t="str">
-        <v>❌ Invalid or duplicate word. Enter a different valid word from the puzzle in CAPS.</v>
-      </c>
-      <c r="I54" t="str">
-        <v>aiml.jpeg</v>
+        <v>regex(., '^[A-Z]+$') and normalize-space(.) = 'WIFI'</v>
+      </c>
+      <c r="H54" t="str">
+        <v>❌ Incorrect decoded word. Enter in UPPERCASE (CAPS ONLY).</v>
       </c>
     </row>
     <row r="55" xml:space="preserve">
@@ -1406,10 +1617,10 @@
         <v>text</v>
       </c>
       <c r="B55" t="str">
-        <v>r4_aiml_destination</v>
+        <v>r3_decode_w4</v>
       </c>
       <c r="C55" t="str" xml:space="preserve">
-        <v xml:space="preserve">Which campus block do these 5 discovered concepts direct your team to?
+        <v xml:space="preserve">Decode Shuffled Word 4: [ SISCUDISNO GGUONLE ] (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D55" t="str">
@@ -1419,207 +1630,247 @@
         <v>yes</v>
       </c>
       <c r="F55" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AIML' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI ML' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AIML BLOCK' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI/ML' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI &amp; ML'</v>
+        <v>❌ Decoding Word 4 is mandatory.</v>
       </c>
       <c r="G55" t="str">
-        <v>❌ Incorrect destination. Deduce the campus block in CAPS from the 5 discovered concepts.</v>
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'DISCUSSION LOUNGE'</v>
       </c>
       <c r="H55" t="str">
-        <v>(translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY')</v>
-      </c>
-      <c r="I55" t="str">
-        <v>aiml.jpeg</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>❌ Incorrect decoded word. Enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+    </row>
+    <row r="56" xml:space="preserve">
       <c r="A56" t="str">
+        <v>text</v>
+      </c>
+      <c r="B56" t="str">
+        <v>r3_decode_w5</v>
+      </c>
+      <c r="C56" t="str" xml:space="preserve">
+        <v xml:space="preserve">Decode Shuffled Word 5: [ IGIDLAT BILRYRA ] (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D56" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E56" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F56" t="str">
+        <v>❌ Decoding Word 5 is mandatory.</v>
+      </c>
+      <c r="G56" t="str">
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'DIGITAL LIBRARY'</v>
+      </c>
+      <c r="H56" t="str">
+        <v>❌ Incorrect decoded word. Enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+    </row>
+    <row r="57" xml:space="preserve">
+      <c r="A57" t="str">
+        <v>text</v>
+      </c>
+      <c r="B57" t="str">
+        <v>r3_lib_loc_answer</v>
+      </c>
+      <c r="C57" t="str" xml:space="preserve">
+        <v xml:space="preserve">Decoded Clues:
+1. ${r3_decode_w1}
+2. ${r3_decode_w2}
+3. ${r3_decode_w3}
+4. ${r3_decode_w4}
+5. ${r3_decode_w5}
+Based on your decoded words, identify the next location: (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D57" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E57" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F57" t="str">
+        <v>❌ Location answer is mandatory.</v>
+      </c>
+      <c r="G57" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'LIBRARY' or normalize-space(.) = 'CENTRAL LIBRARY')</v>
+      </c>
+      <c r="H57" t="str">
+        <v>❌ Incorrect location. Enter the location in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="I57" t="str">
+        <v>(normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY')</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
         <v>end_group</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="str">
+    <row r="59">
+      <c r="A59" t="str">
         <v>begin_group</v>
       </c>
-      <c r="B57" t="str">
-        <v>r4_phy_group</v>
-      </c>
-      <c r="C57" t="str">
-        <v>ROUND 4 — PHYSICAL CHALLENGE</v>
-      </c>
-      <c r="H57" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_admin_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JOHN-CENA' and ${r1_admin_photo} != '' and (translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK') and (((translate(normalize-space(${mba_q1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONOPOLY' and translate(normalize-space(${mba_q2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'YUAN' and translate(normalize-space(${mba_q3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CHIEF EXECUTIVE OFFICER' and translate(normalize-space(${mba_q4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RETURN ON INVESTMENT' and translate(normalize-space(${mba_q5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'B2B' and translate(normalize-space(${mba_q6}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'EQUITY' and translate(normalize-space(${mba_q7}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BULL' and translate(normalize-space(${mba_q8}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'INITIAL PUBLIC OFFERING' and translate(normalize-space(${mba_q9}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GDP' and translate(normalize-space(${mba_q10}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PROMOTION' and ${r2_var1_quickfire_photo} != '') and ${mba_variant_select} = 'mba_01') or (${mba_variant_select} = 'mba_02' and ${r2_var2_quickfire_photo} != '')) and translate(normalize-space(${r2_mba_clearance_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA-QF-1' and (translate(normalize-space(${r3_lib_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(${r3_lib_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY') and (normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' or translate(normalize-space(${r3_lib_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DUMB_FAKE') and ${r3_lib_qr_photo} != '' and (translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AIML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI ML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AIML BLOCK' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI/ML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI &amp; ML')</v>
-      </c>
-    </row>
-    <row r="58" xml:space="preserve">
-      <c r="A58" t="str">
-        <v>note</v>
-      </c>
-      <c r="B58" t="str">
-        <v>r4_phy_note</v>
-      </c>
-      <c r="C58" t="str" xml:space="preserve">
-        <v xml:space="preserve">📍 ROUND 4: PHYSICAL CHALLENGE
-Report immediately to the checkpoint along the pathway!
-Instructions:
-1. Meet the station volunteers.
-2. Complete the physical coordination challenge.
-3. Take a verification photo.
-4. Enter clearance code from the volunteer.
-Enter code in caps</v>
-      </c>
-      <c r="D58" t="str">
-        <v>Complete physical challenge with volunteer.</v>
-      </c>
-    </row>
-    <row r="59" xml:space="preserve">
-      <c r="A59" t="str">
-        <v>image</v>
-      </c>
       <c r="B59" t="str">
-        <v>r4_phy_photo</v>
-      </c>
-      <c r="C59" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Physical Challenge Completion
-Photo upload is mandatory</v>
-      </c>
-      <c r="D59" t="str">
-        <v>Take a clear photo of your team completing the physical coordination challenge.</v>
-      </c>
-      <c r="E59" t="str">
-        <v>yes</v>
+        <v>r3_lib_qr_group</v>
+      </c>
+      <c r="C59" t="str">
+        <v>ROUND 3 — QR HUNT</v>
+      </c>
+      <c r="I59" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY')</v>
       </c>
     </row>
     <row r="60" xml:space="preserve">
       <c r="A60" t="str">
-        <v>text</v>
+        <v>note</v>
       </c>
       <c r="B60" t="str">
-        <v>r4_phy_code</v>
+        <v>r3_lib_qr_note</v>
       </c>
       <c r="C60" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Verification Code
+        <v xml:space="preserve">📍 ROUND 3: QR HUNT
+Go to the location you identified and ask the Luminus volunteer for the next instruction/code.
+Scan the available QR codes and identify the correct one in a fun manner!
 Enter code in caps</v>
       </c>
       <c r="D60" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E60" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F60" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PHY-CY'</v>
-      </c>
-      <c r="G60" t="str">
-        <v>❌ Incorrect verification code. Obtain the code from the station volunteer and enter in CAPS.</v>
+        <v>Locate and scan the correct QR code.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
+        <v>barcode</v>
+      </c>
+      <c r="B61" t="str">
+        <v>r3_lib_qr_scan</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Scan Discovered QR Code (MANDATORY)</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Scan the correct discovered QR code.</v>
+      </c>
+      <c r="E61" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F61" t="str">
+        <v>❌ QR scan is mandatory.</v>
+      </c>
+      <c r="G61" t="str">
+        <v>normalize-space(.) = 'DUMB_FAKE'</v>
+      </c>
+      <c r="H61" t="str">
+        <v>❌ Incorrect QR code scanned. Search for the correct QR code at this station.</v>
+      </c>
+    </row>
+    <row r="62" xml:space="preserve">
+      <c r="A62" t="str">
+        <v>text</v>
+      </c>
+      <c r="B62" t="str">
+        <v>r3_lib_volunteer_code</v>
+      </c>
+      <c r="C62" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Volunteer Completion Code (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D62" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E62" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F62" t="str">
+        <v>❌ Volunteer completion code is mandatory.</v>
+      </c>
+      <c r="G62" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'DUMB_FAKE' or normalize-space(.) = 'LIB-HUNT-GOOD' or normalize-space(.) = 'LIB-PASS' or normalize-space(.) = 'QR-LIB-2')</v>
+      </c>
+      <c r="H62" t="str">
+        <v>❌ Incorrect code. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
+      </c>
+      <c r="I62" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE'</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
         <v>end_group</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="str">
+    <row r="64">
+      <c r="A64" t="str">
         <v>begin_group</v>
       </c>
-      <c r="B62" t="str">
-        <v>final_puzzles_group</v>
-      </c>
-      <c r="C62" t="str">
-        <v>FINAL PUZZLES</v>
-      </c>
-      <c r="H62" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_admin_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JOHN-CENA' and ${r1_admin_photo} != '' and (translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK') and (((translate(normalize-space(${mba_q1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONOPOLY' and translate(normalize-space(${mba_q2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'YUAN' and translate(normalize-space(${mba_q3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CHIEF EXECUTIVE OFFICER' and translate(normalize-space(${mba_q4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RETURN ON INVESTMENT' and translate(normalize-space(${mba_q5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'B2B' and translate(normalize-space(${mba_q6}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'EQUITY' and translate(normalize-space(${mba_q7}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BULL' and translate(normalize-space(${mba_q8}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'INITIAL PUBLIC OFFERING' and translate(normalize-space(${mba_q9}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GDP' and translate(normalize-space(${mba_q10}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PROMOTION' and ${r2_var1_quickfire_photo} != '') and ${mba_variant_select} = 'mba_01') or (${mba_variant_select} = 'mba_02' and ${r2_var2_quickfire_photo} != '')) and translate(normalize-space(${r2_mba_clearance_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA-QF-1' and (translate(normalize-space(${r3_lib_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(${r3_lib_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY') and (normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' or translate(normalize-space(${r3_lib_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DUMB_FAKE') and ${r3_lib_qr_photo} != '' and (translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AIML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI ML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AIML BLOCK' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI/ML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI &amp; ML') and translate(normalize-space(${r4_phy_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PHY-CY' and ${r4_phy_photo} != ''</v>
-      </c>
-    </row>
-    <row r="63" xml:space="preserve">
-      <c r="A63" t="str">
-        <v>note</v>
-      </c>
-      <c r="B63" t="str">
-        <v>final_audi_stage_intro</v>
-      </c>
-      <c r="C63" t="str" xml:space="preserve">
-        <v xml:space="preserve">🏛️ FINAL CHALLENGES
-Proceed to the location and solve the two final riddles!
-Enter code in caps</v>
-      </c>
-      <c r="D63" t="str">
-        <v>Solve the final riddles.</v>
-      </c>
-    </row>
-    <row r="64" xml:space="preserve">
-      <c r="A64" t="str">
-        <v>text</v>
-      </c>
       <c r="B64" t="str">
-        <v>final_riddle1_answer</v>
-      </c>
-      <c r="C64" t="str" xml:space="preserve">
-        <v xml:space="preserve">🧩 RIDDLE 1:
-"I am a place of darkness until the lights ignite. I hold hundreds of red seats, host grand orientations, and echo with voices through microphones. Where are you standing?"
-Enter code in caps</v>
-      </c>
-      <c r="D64" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E64" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F64" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI'</v>
-      </c>
-      <c r="G64" t="str">
-        <v>❌ Incorrect answer. Solve the riddle and enter in CAPS.</v>
+        <v>r4_wordsearch_group</v>
+      </c>
+      <c r="C64" t="str">
+        <v>ROUND 4 LOCATION CLUE</v>
+      </c>
+      <c r="I64" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and (normalize-space(${r3_lib_volunteer_code}) = 'DUMB_FAKE' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-HUNT-GOOD' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-PASS' or normalize-space(${r3_lib_volunteer_code}) = 'QR-LIB-2')</v>
       </c>
     </row>
     <row r="65" xml:space="preserve">
       <c r="A65" t="str">
-        <v>text</v>
+        <v>note</v>
       </c>
       <c r="B65" t="str">
-        <v>final_riddle2_stage_answer</v>
+        <v>r4_wordsearch_intro</v>
       </c>
       <c r="C65" t="str" xml:space="preserve">
-        <v xml:space="preserve">🎭 RIDDLE 2:
-"I am elevated above the crowd, where performers stand and spotlights shine. Underneath my wooden floor or behind the curtains, the ultimate secret waits. What am I?"
+        <v xml:space="preserve">Examine the puzzle image below.
+Find and enter ANY 5 words from the grid amongst:
+• MACHINE LEARNING
+• NEURAL NETWORK
+• PYTHON
+• DATASET
+• ALGORITHM
+• TRAINING DATA
+• DEEP LEARNING
+• DATA MINING
+• MODELING
+• REGRESSION
+• CLASSIFY
 Enter code in caps</v>
       </c>
       <c r="D65" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E65" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F65" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'STAGE'</v>
-      </c>
-      <c r="G65" t="str">
-        <v>❌ Incorrect answer. Solve the stage riddle and enter in CAPS.</v>
-      </c>
-      <c r="H65" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_admin_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JOHN-CENA' and ${r1_admin_photo} != '' and (translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK') and (((translate(normalize-space(${mba_q1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONOPOLY' and translate(normalize-space(${mba_q2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'YUAN' and translate(normalize-space(${mba_q3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CHIEF EXECUTIVE OFFICER' and translate(normalize-space(${mba_q4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RETURN ON INVESTMENT' and translate(normalize-space(${mba_q5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'B2B' and translate(normalize-space(${mba_q6}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'EQUITY' and translate(normalize-space(${mba_q7}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BULL' and translate(normalize-space(${mba_q8}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'INITIAL PUBLIC OFFERING' and translate(normalize-space(${mba_q9}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GDP' and translate(normalize-space(${mba_q10}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PROMOTION' and ${r2_var1_quickfire_photo} != '') and ${mba_variant_select} = 'mba_01') or (${mba_variant_select} = 'mba_02' and ${r2_var2_quickfire_photo} != '')) and translate(normalize-space(${r2_mba_clearance_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA-QF-1' and (translate(normalize-space(${r3_lib_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(${r3_lib_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY') and (normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' or translate(normalize-space(${r3_lib_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DUMB_FAKE') and ${r3_lib_qr_photo} != '' and (translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AIML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI ML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AIML BLOCK' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI/ML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI &amp; ML') and translate(normalize-space(${r4_phy_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PHY-CY' and ${r4_phy_photo} != '' and (translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI')</v>
+        <v>Find 5 words in the image and enter below in CAPS.</v>
+      </c>
+      <c r="J65" t="str">
+        <v>aiml.jpeg</v>
       </c>
     </row>
     <row r="66" xml:space="preserve">
       <c r="A66" t="str">
-        <v>image</v>
+        <v>text</v>
       </c>
       <c r="B66" t="str">
-        <v>final_solved_puzzle_photo</v>
+        <v>r4_ws_word1</v>
       </c>
       <c r="C66" t="str" xml:space="preserve">
-        <v xml:space="preserve">📸 Upload Photo of Your Solved Puzzle
-Photo upload is mandatory</v>
+        <v xml:space="preserve">Enter Discovered Word 1: (MANDATORY)
+Enter code in caps</v>
       </c>
       <c r="D66" t="str">
-        <v>Take a clear photo of your team's completed/solved puzzle.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
       </c>
       <c r="E66" t="str">
         <v>yes</v>
       </c>
+      <c r="F66" t="str">
+        <v>❌ Word 1 is mandatory.</v>
+      </c>
+      <c r="G66" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'MACHINE LEARNING' or normalize-space(.) = 'NEURAL NETWORK' or normalize-space(.) = 'PYTHON' or normalize-space(.) = 'DATASET' or normalize-space(.) = 'ALGORITHM' or normalize-space(.) = 'TRAINING DATA' or normalize-space(.) = 'DEEP LEARNING' or normalize-space(.) = 'DATA MINING' or normalize-space(.) = 'MODELING' or normalize-space(.) = 'REGRESSION' or normalize-space(.) = 'CLASSIFY')</v>
+      </c>
       <c r="H66" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_admin_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JOHN-CENA' and ${r1_admin_photo} != '' and (translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK') and (((translate(normalize-space(${mba_q1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONOPOLY' and translate(normalize-space(${mba_q2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'YUAN' and translate(normalize-space(${mba_q3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CHIEF EXECUTIVE OFFICER' and translate(normalize-space(${mba_q4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RETURN ON INVESTMENT' and translate(normalize-space(${mba_q5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'B2B' and translate(normalize-space(${mba_q6}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'EQUITY' and translate(normalize-space(${mba_q7}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BULL' and translate(normalize-space(${mba_q8}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'INITIAL PUBLIC OFFERING' and translate(normalize-space(${mba_q9}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GDP' and translate(normalize-space(${mba_q10}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PROMOTION' and ${r2_var1_quickfire_photo} != '') and ${mba_variant_select} = 'mba_01') or (${mba_variant_select} = 'mba_02' and ${r2_var2_quickfire_photo} != '')) and translate(normalize-space(${r2_mba_clearance_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA-QF-1' and (translate(normalize-space(${r3_lib_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(${r3_lib_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY') and (normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' or translate(normalize-space(${r3_lib_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DUMB_FAKE') and ${r3_lib_qr_photo} != '' and (translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AIML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI ML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AIML BLOCK' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI/ML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI &amp; ML') and translate(normalize-space(${r4_phy_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PHY-CY' and ${r4_phy_photo} != '' and (translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI') and translate(normalize-space(${final_riddle2_stage_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'STAGE'</v>
+        <v>❌ Invalid word. Enter a valid word found in the puzzle in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="J66" t="str">
+        <v>aiml.jpeg</v>
       </c>
     </row>
     <row r="67" xml:space="preserve">
@@ -1627,10 +1878,10 @@
         <v>text</v>
       </c>
       <c r="B67" t="str">
-        <v>final_stage_volunteer_code</v>
+        <v>r4_ws_word2</v>
       </c>
       <c r="C67" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Final Volunteer Clearance Code
+        <v xml:space="preserve">Enter Discovered Word 2: (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D67" t="str">
@@ -1640,42 +1891,474 @@
         <v>yes</v>
       </c>
       <c r="F67" t="str">
-        <v>translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH2' or translate(normalize-space(.), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH1'</v>
+        <v>❌ Word 2 is mandatory.</v>
       </c>
       <c r="G67" t="str">
-        <v>❌ Incorrect code. Enter the code in CAPS provided by the Chief Judge.</v>
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'MACHINE LEARNING' or normalize-space(.) = 'NEURAL NETWORK' or normalize-space(.) = 'PYTHON' or normalize-space(.) = 'DATASET' or normalize-space(.) = 'ALGORITHM' or normalize-space(.) = 'TRAINING DATA' or normalize-space(.) = 'DEEP LEARNING' or normalize-space(.) = 'DATA MINING' or normalize-space(.) = 'MODELING' or normalize-space(.) = 'REGRESSION' or normalize-space(.) = 'CLASSIFY') and normalize-space(.) != normalize-space(${r4_ws_word1})</v>
       </c>
       <c r="H67" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_admin_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JOHN-CENA' and ${r1_admin_photo} != '' and (translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK') and (((translate(normalize-space(${mba_q1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONOPOLY' and translate(normalize-space(${mba_q2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'YUAN' and translate(normalize-space(${mba_q3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CHIEF EXECUTIVE OFFICER' and translate(normalize-space(${mba_q4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RETURN ON INVESTMENT' and translate(normalize-space(${mba_q5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'B2B' and translate(normalize-space(${mba_q6}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'EQUITY' and translate(normalize-space(${mba_q7}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BULL' and translate(normalize-space(${mba_q8}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'INITIAL PUBLIC OFFERING' and translate(normalize-space(${mba_q9}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GDP' and translate(normalize-space(${mba_q10}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PROMOTION' and ${r2_var1_quickfire_photo} != '') and ${mba_variant_select} = 'mba_01') or (${mba_variant_select} = 'mba_02' and ${r2_var2_quickfire_photo} != '')) and translate(normalize-space(${r2_mba_clearance_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA-QF-1' and (translate(normalize-space(${r3_lib_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(${r3_lib_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY') and (normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' or translate(normalize-space(${r3_lib_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DUMB_FAKE') and ${r3_lib_qr_photo} != '' and (translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AIML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI ML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AIML BLOCK' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI/ML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI &amp; ML') and translate(normalize-space(${r4_phy_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PHY-CY' and ${r4_phy_photo} != '' and (translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI') and translate(normalize-space(${final_riddle2_stage_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'STAGE'</v>
+        <v>❌ Invalid or duplicate word. Enter a different valid word from the puzzle in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="J67" t="str">
+        <v>aiml.jpeg</v>
       </c>
     </row>
     <row r="68" xml:space="preserve">
       <c r="A68" t="str">
+        <v>text</v>
+      </c>
+      <c r="B68" t="str">
+        <v>r4_ws_word3</v>
+      </c>
+      <c r="C68" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Discovered Word 3: (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D68" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E68" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F68" t="str">
+        <v>❌ Word 3 is mandatory.</v>
+      </c>
+      <c r="G68" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'MACHINE LEARNING' or normalize-space(.) = 'NEURAL NETWORK' or normalize-space(.) = 'PYTHON' or normalize-space(.) = 'DATASET' or normalize-space(.) = 'ALGORITHM' or normalize-space(.) = 'TRAINING DATA' or normalize-space(.) = 'DEEP LEARNING' or normalize-space(.) = 'DATA MINING' or normalize-space(.) = 'MODELING' or normalize-space(.) = 'REGRESSION' or normalize-space(.) = 'CLASSIFY') and normalize-space(.) != normalize-space(${r4_ws_word1}) and normalize-space(.) != normalize-space(${r4_ws_word2})</v>
+      </c>
+      <c r="H68" t="str">
+        <v>❌ Invalid or duplicate word. Enter a different valid word from the puzzle in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="J68" t="str">
+        <v>aiml.jpeg</v>
+      </c>
+    </row>
+    <row r="69" xml:space="preserve">
+      <c r="A69" t="str">
+        <v>text</v>
+      </c>
+      <c r="B69" t="str">
+        <v>r4_ws_word4</v>
+      </c>
+      <c r="C69" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Discovered Word 4: (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D69" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E69" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F69" t="str">
+        <v>❌ Word 4 is mandatory.</v>
+      </c>
+      <c r="G69" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'MACHINE LEARNING' or normalize-space(.) = 'NEURAL NETWORK' or normalize-space(.) = 'PYTHON' or normalize-space(.) = 'DATASET' or normalize-space(.) = 'ALGORITHM' or normalize-space(.) = 'TRAINING DATA' or normalize-space(.) = 'DEEP LEARNING' or normalize-space(.) = 'DATA MINING' or normalize-space(.) = 'MODELING' or normalize-space(.) = 'REGRESSION' or normalize-space(.) = 'CLASSIFY') and normalize-space(.) != normalize-space(${r4_ws_word1}) and normalize-space(.) != normalize-space(${r4_ws_word2}) and normalize-space(.) != normalize-space(${r4_ws_word3})</v>
+      </c>
+      <c r="H69" t="str">
+        <v>❌ Invalid or duplicate word. Enter a different valid word from the puzzle in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="J69" t="str">
+        <v>aiml.jpeg</v>
+      </c>
+    </row>
+    <row r="70" xml:space="preserve">
+      <c r="A70" t="str">
+        <v>text</v>
+      </c>
+      <c r="B70" t="str">
+        <v>r4_ws_word5</v>
+      </c>
+      <c r="C70" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Discovered Word 5: (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D70" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E70" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F70" t="str">
+        <v>❌ Word 5 is mandatory.</v>
+      </c>
+      <c r="G70" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'MACHINE LEARNING' or normalize-space(.) = 'NEURAL NETWORK' or normalize-space(.) = 'PYTHON' or normalize-space(.) = 'DATASET' or normalize-space(.) = 'ALGORITHM' or normalize-space(.) = 'TRAINING DATA' or normalize-space(.) = 'DEEP LEARNING' or normalize-space(.) = 'DATA MINING' or normalize-space(.) = 'MODELING' or normalize-space(.) = 'REGRESSION' or normalize-space(.) = 'CLASSIFY') and normalize-space(.) != normalize-space(${r4_ws_word1}) and normalize-space(.) != normalize-space(${r4_ws_word2}) and normalize-space(.) != normalize-space(${r4_ws_word3}) and normalize-space(.) != normalize-space(${r4_ws_word4})</v>
+      </c>
+      <c r="H70" t="str">
+        <v>❌ Invalid or duplicate word. Enter a different valid word from the puzzle in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="J70" t="str">
+        <v>aiml.jpeg</v>
+      </c>
+    </row>
+    <row r="71" xml:space="preserve">
+      <c r="A71" t="str">
+        <v>text</v>
+      </c>
+      <c r="B71" t="str">
+        <v>r4_aiml_destination</v>
+      </c>
+      <c r="C71" t="str" xml:space="preserve">
+        <v xml:space="preserve">Deduce the location related to these words: (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D71" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E71" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F71" t="str">
+        <v>❌ Location answer is mandatory.</v>
+      </c>
+      <c r="G71" t="str">
+        <v>regex(., '^[A-Z0-9\/&amp; ]+$') and (normalize-space(.) = 'AIML' or normalize-space(.) = 'AI ML' or normalize-space(.) = 'AIML BLOCK' or normalize-space(.) = 'AI/ML' or normalize-space(.) = 'AI &amp; ML')</v>
+      </c>
+      <c r="H71" t="str">
+        <v>❌ Incorrect destination. Enter the location in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="I71" t="str">
+        <v>(normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY')</v>
+      </c>
+      <c r="J71" t="str">
+        <v>aiml.jpeg</v>
+      </c>
+    </row>
+    <row r="72" xml:space="preserve">
+      <c r="A72" t="str">
         <v>note</v>
       </c>
-      <c r="B68" t="str">
+      <c r="B72" t="str">
+        <v>r4_proceed_note</v>
+      </c>
+      <c r="C72" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏃 Go to the location you identified and ask the Luminus volunteer for the START CODE.
+Enter code in caps</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Go to the location and ask volunteer for start code.</v>
+      </c>
+      <c r="I72" t="str">
+        <v>(normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML')</v>
+      </c>
+    </row>
+    <row r="73" xml:space="preserve">
+      <c r="A73" t="str">
+        <v>text</v>
+      </c>
+      <c r="B73" t="str">
+        <v>r4_start_code</v>
+      </c>
+      <c r="C73" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter START CODE from Volunteer (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D73" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E73" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F73" t="str">
+        <v>❌ START CODE is mandatory.</v>
+      </c>
+      <c r="G73" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'START-AI-PHY' or normalize-space(.) = 'START-PHY')</v>
+      </c>
+      <c r="H73" t="str">
+        <v>❌ Incorrect START CODE. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
+      </c>
+      <c r="I73" t="str">
+        <v>(normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML')</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>begin_group</v>
+      </c>
+      <c r="B75" t="str">
+        <v>r4_phy_group</v>
+      </c>
+      <c r="C75" t="str">
+        <v>ROUND 4 — PHYSICAL CHALLENGE</v>
+      </c>
+      <c r="I75" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and (normalize-space(${r3_lib_volunteer_code}) = 'DUMB_FAKE' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-HUNT-GOOD' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-PASS' or normalize-space(${r3_lib_volunteer_code}) = 'QR-LIB-2') and (normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY')</v>
+      </c>
+    </row>
+    <row r="76" xml:space="preserve">
+      <c r="A76" t="str">
+        <v>note</v>
+      </c>
+      <c r="B76" t="str">
+        <v>r4_phy_note</v>
+      </c>
+      <c r="C76" t="str" xml:space="preserve">
+        <v xml:space="preserve">📍 ROUND 4: PHYSICAL CHALLENGE
+Perform the physical challenge as instructed by the station volunteer.
+Once completed, collect the finish code from the volunteer.
+Enter code in caps</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Complete physical challenge with volunteer.</v>
+      </c>
+    </row>
+    <row r="77" xml:space="preserve">
+      <c r="A77" t="str">
+        <v>image</v>
+      </c>
+      <c r="B77" t="str">
+        <v>r4_phy_photo</v>
+      </c>
+      <c r="C77" t="str" xml:space="preserve">
+        <v xml:space="preserve">📸 Upload Photo of Physical Challenge Completion (MANDATORY)
+Photo upload is mandatory</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Take a clear photo of your team completing the physical coordination challenge.</v>
+      </c>
+      <c r="E77" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F77" t="str">
+        <v>❌ Photo upload of the challenge is mandatory.</v>
+      </c>
+    </row>
+    <row r="78" xml:space="preserve">
+      <c r="A78" t="str">
+        <v>text</v>
+      </c>
+      <c r="B78" t="str">
+        <v>r4_phy_code</v>
+      </c>
+      <c r="C78" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter END CODE from Volunteer (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D78" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E78" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F78" t="str">
+        <v>❌ END CODE is mandatory.</v>
+      </c>
+      <c r="G78" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'PHY-AIML' or normalize-space(.) = 'PHY-CY')</v>
+      </c>
+      <c r="H78" t="str">
+        <v>❌ Incorrect END CODE. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>end_group</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>begin_group</v>
+      </c>
+      <c r="B80" t="str">
+        <v>final_puzzles_group</v>
+      </c>
+      <c r="C80" t="str">
+        <v>FINAL ROUND</v>
+      </c>
+      <c r="I80" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and (normalize-space(${r3_lib_volunteer_code}) = 'DUMB_FAKE' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-HUNT-GOOD' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-PASS' or normalize-space(${r3_lib_volunteer_code}) = 'QR-LIB-2') and (normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != ''</v>
+      </c>
+    </row>
+    <row r="81" xml:space="preserve">
+      <c r="A81" t="str">
+        <v>note</v>
+      </c>
+      <c r="B81" t="str">
+        <v>final_audi_stage_intro</v>
+      </c>
+      <c r="C81" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏛️ FINAL ROUND — RIDDLES
+Solve the two final riddles to reveal the final destination!
+Enter code in caps</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Solve the final riddles in CAPS.</v>
+      </c>
+    </row>
+    <row r="82" xml:space="preserve">
+      <c r="A82" t="str">
+        <v>text</v>
+      </c>
+      <c r="B82" t="str">
+        <v>final_riddle1_answer</v>
+      </c>
+      <c r="C82" t="str" xml:space="preserve">
+        <v xml:space="preserve">🧩 AUDITORIUM RIDDLE: (MANDATORY)
+"I am empty, yet I am built for crowds.
+I have a stage, but no actors of my own.
+I have countless seats, but none are meant to sleep.
+When a voice rises before me, silence falls behind me.
+When the lights awaken, all eyes face one direction.
+What am I?"
+Enter code in caps</v>
+      </c>
+      <c r="D82" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E82" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F82" t="str">
+        <v>❌ Solving Riddle 1 is mandatory.</v>
+      </c>
+      <c r="G82" t="str">
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'AUDITORIUM' or normalize-space(.) = 'AUDI')</v>
+      </c>
+      <c r="H82" t="str">
+        <v>❌ Incorrect answer. Solve Riddle 1 and enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+    </row>
+    <row r="83" xml:space="preserve">
+      <c r="A83" t="str">
+        <v>text</v>
+      </c>
+      <c r="B83" t="str">
+        <v>final_riddle2_stage_answer</v>
+      </c>
+      <c r="C83" t="str" xml:space="preserve">
+        <v xml:space="preserve">🎭 STAGE RIDDLE: (MANDATORY)
+"I am elevated above the crowd, where performers stand and spotlights shine.
+Underneath my wooden floor or behind the curtains, the ultimate secret waits.
+What am I?"
+Enter code in caps</v>
+      </c>
+      <c r="D83" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E83" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F83" t="str">
+        <v>❌ Solving Riddle 2 is mandatory.</v>
+      </c>
+      <c r="G83" t="str">
+        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'STAGE'</v>
+      </c>
+      <c r="H83" t="str">
+        <v>❌ Incorrect answer. Solve Riddle 2 and enter in UPPERCASE (CAPS ONLY).</v>
+      </c>
+      <c r="I83" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and (normalize-space(${r3_lib_volunteer_code}) = 'DUMB_FAKE' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-HUNT-GOOD' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-PASS' or normalize-space(${r3_lib_volunteer_code}) = 'QR-LIB-2') and (normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI')</v>
+      </c>
+    </row>
+    <row r="84" xml:space="preserve">
+      <c r="A84" t="str">
+        <v>note</v>
+      </c>
+      <c r="B84" t="str">
+        <v>final_proceed_stage_note</v>
+      </c>
+      <c r="C84" t="str" xml:space="preserve">
+        <v xml:space="preserve">🏃 Proceed to the final location identified!
+Solve the final puzzle at the stage, upload a photo of the completed puzzle, and get your clearance code from the Chief Judge!
+Enter code in caps</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Go to the stage to solve the final puzzle.</v>
+      </c>
+      <c r="I84" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and (normalize-space(${r3_lib_volunteer_code}) = 'DUMB_FAKE' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-HUNT-GOOD' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-PASS' or normalize-space(${r3_lib_volunteer_code}) = 'QR-LIB-2') and (normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+      </c>
+    </row>
+    <row r="85" xml:space="preserve">
+      <c r="A85" t="str">
+        <v>image</v>
+      </c>
+      <c r="B85" t="str">
+        <v>final_solved_puzzle_photo</v>
+      </c>
+      <c r="C85" t="str" xml:space="preserve">
+        <v xml:space="preserve">📸 Upload Photo of Your Solved Puzzle (MANDATORY)
+Photo upload is mandatory</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Take a clear photo of your team's completed/solved puzzle.</v>
+      </c>
+      <c r="E85" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F85" t="str">
+        <v>❌ Photo of the solved puzzle is mandatory.</v>
+      </c>
+      <c r="I85" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and (normalize-space(${r3_lib_volunteer_code}) = 'DUMB_FAKE' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-HUNT-GOOD' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-PASS' or normalize-space(${r3_lib_volunteer_code}) = 'QR-LIB-2') and (normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+      </c>
+    </row>
+    <row r="86" xml:space="preserve">
+      <c r="A86" t="str">
+        <v>text</v>
+      </c>
+      <c r="B86" t="str">
+        <v>final_stage_volunteer_code</v>
+      </c>
+      <c r="C86" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Final Volunteer Clearance Code (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D86" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+      </c>
+      <c r="E86" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F86" t="str">
+        <v>❌ Final clearance code is mandatory.</v>
+      </c>
+      <c r="G86" t="str">
+        <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'FINAL-PATH2' or normalize-space(.) = 'FINAL-PATH1')</v>
+      </c>
+      <c r="H86" t="str">
+        <v>❌ Incorrect code. Enter the code in UPPERCASE (CAPS ONLY) provided by the Chief Judge.</v>
+      </c>
+      <c r="I86" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and (normalize-space(${r3_lib_volunteer_code}) = 'DUMB_FAKE' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-HUNT-GOOD' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-PASS' or normalize-space(${r3_lib_volunteer_code}) = 'QR-LIB-2') and (normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+      </c>
+    </row>
+    <row r="87" xml:space="preserve">
+      <c r="A87" t="str">
+        <v>note</v>
+      </c>
+      <c r="B87" t="str">
         <v>final_congratulations_screen</v>
       </c>
-      <c r="C68" t="str" xml:space="preserve">
-        <v xml:space="preserve">🎉 CONGRATULATIONS! PATH 2 COMPLETED.
-🏆 You have successfully conquered every challenge, puzzle, and cipher on PATH 2!
-Show this completion screen immediately to the Chief Judge to lock in your finishing timestamp and rank!</v>
-      </c>
-      <c r="D68" t="str">
-        <v>Report to Chief Judge to finalize completion.</v>
-      </c>
-      <c r="H68" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and translate(normalize-space(${r1_admin_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'JOHN-CENA' and ${r1_admin_photo} != '' and (translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA' or translate(normalize-space(${r2_mba_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA BLOCK') and (((translate(normalize-space(${mba_q1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MONOPOLY' and translate(normalize-space(${mba_q2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'YUAN' and translate(normalize-space(${mba_q3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CHIEF EXECUTIVE OFFICER' and translate(normalize-space(${mba_q4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'RETURN ON INVESTMENT' and translate(normalize-space(${mba_q5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'B2B' and translate(normalize-space(${mba_q6}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'EQUITY' and translate(normalize-space(${mba_q7}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'BULL' and translate(normalize-space(${mba_q8}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'INITIAL PUBLIC OFFERING' and translate(normalize-space(${mba_q9}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'GDP' and translate(normalize-space(${mba_q10}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PROMOTION' and ${r2_var1_quickfire_photo} != '') and ${mba_variant_select} = 'mba_01') or (${mba_variant_select} = 'mba_02' and ${r2_var2_quickfire_photo} != '')) and translate(normalize-space(${r2_mba_clearance_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MBA-QF-1' and (translate(normalize-space(${r3_lib_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'LIBRARY' or translate(normalize-space(${r3_lib_loc_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CENTRAL LIBRARY') and (normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' or translate(normalize-space(${r3_lib_qr_scan}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DUMB_FAKE') and ${r3_lib_qr_photo} != '' and (translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word1}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word2}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word3}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word4}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MACHINE LEARNING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'NEURAL NETWORK' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PYTHON' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATASET' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'ALGORITHM' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'TRAINING DATA' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DEEP LEARNING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'DATA MINING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'MODELING' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'REGRESSION' or translate(normalize-space(${r4_ws_word5}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'CLASSIFY') and (translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AIML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI ML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AIML BLOCK' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI/ML' or translate(normalize-space(${r4_aiml_destination}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AI &amp; ML') and translate(normalize-space(${r4_phy_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'PHY-CY' and ${r4_phy_photo} != '' and (translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDITORIUM' or translate(normalize-space(${final_riddle1_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'AUDI') and translate(normalize-space(${final_riddle2_stage_answer}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'STAGE' and (translate(normalize-space(${final_stage_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH2' or translate(normalize-space(${final_stage_volunteer_code}), 'abcdefghijklmnopqrstuvwxyz', 'ABCDEFGHIJKLMNOPQRSTUVWXYZ') = 'FINAL-PATH1') and ${final_solved_puzzle_photo} != ''</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
+      <c r="C87" t="str" xml:space="preserve">
+        <v xml:space="preserve">🎉 CONGRATULATIONS! YOU HAVE COMPLETED PATH 2!
+🏆 You have successfully entered the final clearance code!
+🔔 NOW RUN TO GO RING THE BELL TO WIN THE GAME! 🔔🏃💨</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Run to ring the bell to claim victory!</v>
+      </c>
+      <c r="I87" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and (normalize-space(${r3_lib_volunteer_code}) = 'DUMB_FAKE' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-HUNT-GOOD' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-PASS' or normalize-space(${r3_lib_volunteer_code}) = 'QR-LIB-2') and (normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE' and (normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH2' or normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH1') and ${final_solved_puzzle_photo} != ''</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
         <v>end_group</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J88"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1700,10 +2383,10 @@
         <v>mba_variants</v>
       </c>
       <c r="B2" t="str">
-        <v>mba_01</v>
+        <v>var_a</v>
       </c>
       <c r="C2" t="str">
-        <v>Variant 1: MBA Quickfire (Set A)</v>
+        <v>Variant A</v>
       </c>
     </row>
     <row r="3">
@@ -1711,10 +2394,10 @@
         <v>mba_variants</v>
       </c>
       <c r="B3" t="str">
-        <v>mba_02</v>
+        <v>var_b</v>
       </c>
       <c r="C3" t="str">
-        <v>Variant 2: MBA Quickfire (Set B)</v>
+        <v>Variant B</v>
       </c>
     </row>
   </sheetData>
@@ -1750,7 +2433,7 @@
         <v>final_clue_path2</v>
       </c>
       <c r="C2" t="str">
-        <v>20260902</v>
+        <v>20260904</v>
       </c>
       <c r="D2" t="str">
         <v>default</v>

--- a/ROUTE_2_PATH2_ADMIN_MBA_LIB_AIML_AUDI/PATH2_FINAL_ODK.xlsx
+++ b/ROUTE_2_PATH2_ADMIN_MBA_LIB_AIML_AUDI/PATH2_FINAL_ODK.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:K88"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,6 +431,9 @@
       </c>
       <c r="J1" t="str">
         <v>media::image</v>
+      </c>
+      <c r="K1" t="str">
+        <v>appearance</v>
       </c>
     </row>
     <row r="2">
@@ -483,7 +486,8 @@
 * Next 15 teams proceed to Round 3.
 * Next 7 teams proceed to Round 4.
 * Next 2 teams proceed to Round 5.
-⚠️ MANDATORY RESPONSE &amp; CAPS ONLY RULES:
+⚠️ STRICT PROGRESSION &amp; MANDATORY RULES:
+• Read each question properly as you cannot come back to the question once you go ahead!
 • Every single question, photo upload, and code entry is strictly MANDATORY.
 • All text answers and volunteer codes must be entered in UPPERCASE (CAPS ONLY).
 • Lowercase letters will be rejected by validation.</v>
@@ -504,7 +508,7 @@
 Enter code in caps</v>
       </c>
       <c r="D4" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E4" t="str">
         <v>yes</v>
@@ -531,7 +535,7 @@
 Enter code in caps</v>
       </c>
       <c r="D5" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E5" t="str">
         <v>yes</v>
@@ -639,7 +643,7 @@
 Enter code in caps</v>
       </c>
       <c r="D11" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E11" t="str">
         <v>yes</v>
@@ -701,7 +705,7 @@
 Enter code in caps</v>
       </c>
       <c r="D15" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E15" t="str">
         <v>yes</v>
@@ -746,7 +750,7 @@
 Enter code in caps</v>
       </c>
       <c r="D17" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E17" t="str">
         <v>yes</v>
@@ -846,7 +850,7 @@
 Enter code in caps</v>
       </c>
       <c r="D23" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E23" t="str">
         <v>yes</v>
@@ -873,7 +877,7 @@
 Enter code in caps</v>
       </c>
       <c r="D24" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E24" t="str">
         <v>yes</v>
@@ -900,7 +904,7 @@
 Enter code in caps</v>
       </c>
       <c r="D25" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E25" t="str">
         <v>yes</v>
@@ -927,7 +931,7 @@
 Enter code in caps</v>
       </c>
       <c r="D26" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E26" t="str">
         <v>yes</v>
@@ -954,7 +958,7 @@
 Enter code in caps</v>
       </c>
       <c r="D27" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E27" t="str">
         <v>yes</v>
@@ -981,7 +985,7 @@
 Enter code in caps</v>
       </c>
       <c r="D28" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E28" t="str">
         <v>yes</v>
@@ -1008,7 +1012,7 @@
 Enter code in caps</v>
       </c>
       <c r="D29" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E29" t="str">
         <v>yes</v>
@@ -1035,7 +1039,7 @@
 Enter code in caps</v>
       </c>
       <c r="D30" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E30" t="str">
         <v>yes</v>
@@ -1062,7 +1066,7 @@
 Enter code in caps</v>
       </c>
       <c r="D31" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E31" t="str">
         <v>yes</v>
@@ -1089,7 +1093,7 @@
 Enter code in caps</v>
       </c>
       <c r="D32" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E32" t="str">
         <v>yes</v>
@@ -1116,7 +1120,7 @@
 Enter code in caps</v>
       </c>
       <c r="D33" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E33" t="str">
         <v>yes</v>
@@ -1181,7 +1185,7 @@
 Enter code in caps</v>
       </c>
       <c r="D37" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E37" t="str">
         <v>yes</v>
@@ -1190,7 +1194,7 @@
         <v>❌ Question 1 is mandatory.</v>
       </c>
       <c r="G37" t="str">
-        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'BAMBALONI'</v>
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'BAMBALONI' or normalize-space(.) = 'BAMBOULONI' or normalize-space(.) = 'BAMBALOUNI')</v>
       </c>
       <c r="H37" t="str">
         <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
@@ -1198,6 +1202,9 @@
       <c r="J37" t="str">
         <v>bambaloni.jpeg</v>
       </c>
+      <c r="K37" t="str">
+        <v>big-image</v>
+      </c>
     </row>
     <row r="38" xml:space="preserve">
       <c r="A38" t="str">
@@ -1211,7 +1218,7 @@
 Enter code in caps</v>
       </c>
       <c r="D38" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E38" t="str">
         <v>yes</v>
@@ -1238,7 +1245,7 @@
 Enter code in caps</v>
       </c>
       <c r="D39" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E39" t="str">
         <v>yes</v>
@@ -1247,7 +1254,7 @@
         <v>❌ Question 3 is mandatory.</v>
       </c>
       <c r="G39" t="str">
-        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'HORRID HENRY'</v>
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'HORRID HENRY' or normalize-space(.) = 'HORRIDHENRY')</v>
       </c>
       <c r="H39" t="str">
         <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
@@ -1255,6 +1262,9 @@
       <c r="J39" t="str">
         <v>horrid henry.jpeg</v>
       </c>
+      <c r="K39" t="str">
+        <v>big-image</v>
+      </c>
     </row>
     <row r="40" xml:space="preserve">
       <c r="A40" t="str">
@@ -1268,7 +1278,7 @@
 Enter code in caps</v>
       </c>
       <c r="D40" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E40" t="str">
         <v>yes</v>
@@ -1277,7 +1287,7 @@
         <v>❌ Question 4 is mandatory.</v>
       </c>
       <c r="G40" t="str">
-        <v>regex(., '^[A-Z0-9 ]+$') and (normalize-space(.) = '5 STAR' or normalize-space(.) = '5STAR' or normalize-space(.) = 'FIVE STAR')</v>
+        <v>regex(., '^[A-Z0-9\- ]+$') and (normalize-space(.) = '5 STAR' or normalize-space(.) = '5STAR' or normalize-space(.) = 'FIVE STAR' or normalize-space(.) = 'FIVE-STAR' or normalize-space(.) = '5-STAR')</v>
       </c>
       <c r="H40" t="str">
         <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
@@ -1285,6 +1295,9 @@
       <c r="J40" t="str">
         <v>5 star.jpeg</v>
       </c>
+      <c r="K40" t="str">
+        <v>big-image</v>
+      </c>
     </row>
     <row r="41" xml:space="preserve">
       <c r="A41" t="str">
@@ -1298,7 +1311,7 @@
 Enter code in caps</v>
       </c>
       <c r="D41" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E41" t="str">
         <v>yes</v>
@@ -1315,6 +1328,9 @@
       <c r="J41" t="str">
         <v>nokia.jpeg</v>
       </c>
+      <c r="K41" t="str">
+        <v>big-image</v>
+      </c>
     </row>
     <row r="42" xml:space="preserve">
       <c r="A42" t="str">
@@ -1328,7 +1344,7 @@
 Enter code in caps</v>
       </c>
       <c r="D42" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E42" t="str">
         <v>yes</v>
@@ -1345,6 +1361,9 @@
       <c r="J42" t="str">
         <v>durian.jpeg</v>
       </c>
+      <c r="K42" t="str">
+        <v>big-image</v>
+      </c>
     </row>
     <row r="43" xml:space="preserve">
       <c r="A43" t="str">
@@ -1358,7 +1377,7 @@
 Enter code in caps</v>
       </c>
       <c r="D43" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E43" t="str">
         <v>yes</v>
@@ -1367,7 +1386,7 @@
         <v>❌ Question 7 is mandatory.</v>
       </c>
       <c r="G43" t="str">
-        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'VODAFONE'</v>
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'VODAFONE' or normalize-space(.) = 'HUTCH')</v>
       </c>
       <c r="H43" t="str">
         <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
@@ -1385,7 +1404,7 @@
 Enter code in caps</v>
       </c>
       <c r="D44" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E44" t="str">
         <v>yes</v>
@@ -1394,7 +1413,7 @@
         <v>❌ Question 8 is mandatory.</v>
       </c>
       <c r="G44" t="str">
-        <v>regex(., '^[A-Z ]+$') and normalize-space(.) = 'MICHELIN'</v>
+        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'MICHELIN' or normalize-space(.) = 'MICHELIN MAN' or normalize-space(.) = 'BIBENDUM')</v>
       </c>
       <c r="H44" t="str">
         <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
@@ -1402,6 +1421,9 @@
       <c r="J44" t="str">
         <v>michelin.jpeg</v>
       </c>
+      <c r="K44" t="str">
+        <v>big-image</v>
+      </c>
     </row>
     <row r="45" xml:space="preserve">
       <c r="A45" t="str">
@@ -1415,7 +1437,7 @@
 Enter code in caps</v>
       </c>
       <c r="D45" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E45" t="str">
         <v>yes</v>
@@ -1424,7 +1446,7 @@
         <v>❌ Question 9 is mandatory.</v>
       </c>
       <c r="G45" t="str">
-        <v>regex(., '^[A-Z0-9\.\- ]+$') and (normalize-space(.) = 'DR. RAMA NAGAPPA SHETTY' or normalize-space(.) = 'RAMA NAGAPPA SHETTY' or normalize-space(.) = 'DR RAMA NAGAPPA SHETTY')</v>
+        <v>regex(., '^[A-Z0-9\.\- ]+$') and (normalize-space(.) = 'DR. RAMA NAGAPPA SHETTY' or normalize-space(.) = 'RAMA NAGAPPA SHETTY' or normalize-space(.) = 'DR RAMA NAGAPPA SHETTY' or normalize-space(.) = 'RAM NAGAPPA SHETTY' or normalize-space(.) = 'RN SHETTY' or normalize-space(.) = 'R N SHETTY')</v>
       </c>
       <c r="H45" t="str">
         <v>❌ Incorrect answer. Please enter in UPPERCASE (CAPS ONLY).</v>
@@ -1442,7 +1464,7 @@
 Enter code in caps</v>
       </c>
       <c r="D46" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E46" t="str">
         <v>yes</v>
@@ -1459,6 +1481,9 @@
       <c r="J46" t="str">
         <v>palmonas.jpeg</v>
       </c>
+      <c r="K46" t="str">
+        <v>big-image</v>
+      </c>
     </row>
     <row r="47" xml:space="preserve">
       <c r="A47" t="str">
@@ -1472,7 +1497,7 @@
 Enter code in caps</v>
       </c>
       <c r="D47" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E47" t="str">
         <v>yes</v>
@@ -1481,13 +1506,13 @@
         <v>❌ Completion code is mandatory.</v>
       </c>
       <c r="G47" t="str">
-        <v>regex(., '^[A-Z0-9\-_]+$') and normalize-space(.) = 'MB-BQ-2'</v>
+        <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'MBA-BQ-2' or normalize-space(.) = 'MB-BQ-2' or normalize-space(.) = 'MBA_BQ_2' or normalize-space(.) = 'MB_BQ_2')</v>
       </c>
       <c r="H47" t="str">
         <v>❌ Incorrect completion code. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
       </c>
       <c r="I47" t="str">
-        <v>(normalize-space(${r2_b_q1}) = 'BAMBALONI' and normalize-space(${r2_b_q2}) = 'APPLE' and normalize-space(${r2_b_q3}) = 'HORRID HENRY' and (normalize-space(${r2_b_q4}) = '5 STAR' or normalize-space(${r2_b_q4}) = '5STAR' or normalize-space(${r2_b_q4}) = 'FIVE STAR') and normalize-space(${r2_b_q5}) = 'NOKIA' and normalize-space(${r2_b_q6}) = 'DURIAN' and normalize-space(${r2_b_q7}) = 'VODAFONE' and normalize-space(${r2_b_q8}) = 'MICHELIN' and (normalize-space(${r2_b_q9}) = 'DR. RAMA NAGAPPA SHETTY' or normalize-space(${r2_b_q9}) = 'RAMA NAGAPPA SHETTY' or normalize-space(${r2_b_q9}) = 'DR RAMA NAGAPPA SHETTY') and normalize-space(${r2_b_q10}) = 'PALMONAS')</v>
+        <v>((normalize-space(${r2_b_q1}) = 'BAMBALONI' or normalize-space(${r2_b_q1}) = 'BAMBOULONI' or normalize-space(${r2_b_q1}) = 'BAMBALOUNI') and normalize-space(${r2_b_q2}) = 'APPLE' and (normalize-space(${r2_b_q3}) = 'HORRID HENRY' or normalize-space(${r2_b_q3}) = 'HORRIDHENRY') and (normalize-space(${r2_b_q4}) = '5 STAR' or normalize-space(${r2_b_q4}) = '5STAR' or normalize-space(${r2_b_q4}) = 'FIVE STAR' or normalize-space(${r2_b_q4}) = 'FIVE-STAR' or normalize-space(${r2_b_q4}) = '5-STAR') and normalize-space(${r2_b_q5}) = 'NOKIA' and normalize-space(${r2_b_q6}) = 'DURIAN' and (normalize-space(${r2_b_q7}) = 'VODAFONE' or normalize-space(${r2_b_q7}) = 'HUTCH') and (normalize-space(${r2_b_q8}) = 'MICHELIN' or normalize-space(${r2_b_q8}) = 'MICHELIN MAN' or normalize-space(${r2_b_q8}) = 'BIBENDUM') and (normalize-space(${r2_b_q9}) = 'DR. RAMA NAGAPPA SHETTY' or normalize-space(${r2_b_q9}) = 'RAMA NAGAPPA SHETTY' or normalize-space(${r2_b_q9}) = 'DR RAMA NAGAPPA SHETTY' or normalize-space(${r2_b_q9}) = 'RAM NAGAPPA SHETTY' or normalize-space(${r2_b_q9}) = 'RN SHETTY' or normalize-space(${r2_b_q9}) = 'R N SHETTY') and normalize-space(${r2_b_q10}) = 'PALMONAS')</v>
       </c>
     </row>
     <row r="48">
@@ -1511,7 +1536,7 @@
         <v>ROUND 3</v>
       </c>
       <c r="I50" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2'))</v>
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and (normalize-space(${r2_var_a_code}) = 'MBA-QF-1' or normalize-space(${r2_var_a_code}) = 'MB-QF-1' or normalize-space(${r2_var_a_code}) = 'MBA_QF_1')) or (${mba_variant_select} = 'var_b' and (normalize-space(${r2_var_b_code}) = 'MBA-BQ-2' or normalize-space(${r2_var_b_code}) = 'MB-BQ-2' or normalize-space(${r2_var_b_code}) = 'MBA_BQ_2' or normalize-space(${r2_var_b_code}) = 'MB_BQ_2')))</v>
       </c>
     </row>
     <row r="51" xml:space="preserve">
@@ -1543,7 +1568,7 @@
 Enter code in caps</v>
       </c>
       <c r="D52" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E52" t="str">
         <v>yes</v>
@@ -1570,7 +1595,7 @@
 Enter code in caps</v>
       </c>
       <c r="D53" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E53" t="str">
         <v>yes</v>
@@ -1597,7 +1622,7 @@
 Enter code in caps</v>
       </c>
       <c r="D54" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E54" t="str">
         <v>yes</v>
@@ -1624,7 +1649,7 @@
 Enter code in caps</v>
       </c>
       <c r="D55" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E55" t="str">
         <v>yes</v>
@@ -1651,7 +1676,7 @@
 Enter code in caps</v>
       </c>
       <c r="D56" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E56" t="str">
         <v>yes</v>
@@ -1684,7 +1709,7 @@
 Enter code in caps</v>
       </c>
       <c r="D57" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E57" t="str">
         <v>yes</v>
@@ -1718,7 +1743,7 @@
         <v>ROUND 3 — QR HUNT</v>
       </c>
       <c r="I59" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY')</v>
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and (normalize-space(${r2_var_a_code}) = 'MBA-QF-1' or normalize-space(${r2_var_a_code}) = 'MB-QF-1' or normalize-space(${r2_var_a_code}) = 'MBA_QF_1')) or (${mba_variant_select} = 'var_b' and (normalize-space(${r2_var_b_code}) = 'MBA-BQ-2' or normalize-space(${r2_var_b_code}) = 'MB-BQ-2' or normalize-space(${r2_var_b_code}) = 'MBA_BQ_2' or normalize-space(${r2_var_b_code}) = 'MB_BQ_2'))) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY')</v>
       </c>
     </row>
     <row r="60" xml:space="preserve">
@@ -1730,7 +1755,7 @@
       </c>
       <c r="C60" t="str" xml:space="preserve">
         <v xml:space="preserve">📍 ROUND 3: QR HUNT
-Go to the location you identified and ask the Luminus volunteer for the next instruction/code.
+Go to the location you identified.
 Scan the available QR codes and identify the correct one in a fun manner!
 Enter code in caps</v>
       </c>
@@ -1764,65 +1789,192 @@
         <v>❌ Incorrect QR code scanned. Search for the correct QR code at this station.</v>
       </c>
     </row>
-    <row r="62" xml:space="preserve">
+    <row r="62">
       <c r="A62" t="str">
-        <v>text</v>
-      </c>
-      <c r="B62" t="str">
-        <v>r3_lib_volunteer_code</v>
-      </c>
-      <c r="C62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Volunteer Completion Code (MANDATORY)
-Enter code in caps</v>
-      </c>
-      <c r="D62" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E62" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F62" t="str">
-        <v>❌ Volunteer completion code is mandatory.</v>
-      </c>
-      <c r="G62" t="str">
-        <v>regex(., '^[A-Z0-9\-_]+$') and (normalize-space(.) = 'DUMB_FAKE' or normalize-space(.) = 'LIB-HUNT-GOOD' or normalize-space(.) = 'LIB-PASS' or normalize-space(.) = 'QR-LIB-2')</v>
-      </c>
-      <c r="H62" t="str">
-        <v>❌ Incorrect code. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
-      </c>
-      <c r="I62" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE'</v>
+        <v>end_group</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>end_group</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>begin_group</v>
+      </c>
+      <c r="B63" t="str">
+        <v>r4_wordsearch_group</v>
+      </c>
+      <c r="C63" t="str">
+        <v>ROUND 4 LOCATION CLUE</v>
+      </c>
+      <c r="I63" t="str">
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and (normalize-space(${r2_var_a_code}) = 'MBA-QF-1' or normalize-space(${r2_var_a_code}) = 'MB-QF-1' or normalize-space(${r2_var_a_code}) = 'MBA_QF_1')) or (${mba_variant_select} = 'var_b' and (normalize-space(${r2_var_b_code}) = 'MBA-BQ-2' or normalize-space(${r2_var_b_code}) = 'MB-BQ-2' or normalize-space(${r2_var_b_code}) = 'MBA_BQ_2' or normalize-space(${r2_var_b_code}) = 'MB_BQ_2'))) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE'</v>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
       <c r="A64" t="str">
-        <v>begin_group</v>
+        <v>note</v>
       </c>
       <c r="B64" t="str">
-        <v>r4_wordsearch_group</v>
-      </c>
-      <c r="C64" t="str">
-        <v>ROUND 4 LOCATION CLUE</v>
-      </c>
-      <c r="I64" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and (normalize-space(${r3_lib_volunteer_code}) = 'DUMB_FAKE' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-HUNT-GOOD' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-PASS' or normalize-space(${r3_lib_volunteer_code}) = 'QR-LIB-2')</v>
+        <v>r4_wordsearch_intro</v>
+      </c>
+      <c r="C64" t="str" xml:space="preserve">
+        <v xml:space="preserve">Examine the puzzle image below.
+Find and enter ANY 5 words hidden within the grid that you can see.
+Enter code in caps</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Examine the grid and enter 5 words you can find in CAPS.</v>
+      </c>
+      <c r="J64" t="str">
+        <v>aiml.jpeg</v>
+      </c>
+      <c r="K64" t="str">
+        <v>big-image</v>
       </c>
     </row>
     <row r="65" xml:space="preserve">
       <c r="A65" t="str">
+        <v>text</v>
+      </c>
+      <c r="B65" t="str">
+        <v>r4_ws_word1</v>
+      </c>
+      <c r="C65" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Discovered Word 1: (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D65" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E65" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F65" t="str">
+        <v>❌ Word 1 is mandatory.</v>
+      </c>
+      <c r="J65" t="str">
+        <v>aiml.jpeg</v>
+      </c>
+      <c r="K65" t="str">
+        <v>big-image</v>
+      </c>
+    </row>
+    <row r="66" xml:space="preserve">
+      <c r="A66" t="str">
+        <v>text</v>
+      </c>
+      <c r="B66" t="str">
+        <v>r4_ws_word2</v>
+      </c>
+      <c r="C66" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Discovered Word 2: (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D66" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E66" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F66" t="str">
+        <v>❌ Word 2 is mandatory.</v>
+      </c>
+      <c r="J66" t="str">
+        <v>aiml.jpeg</v>
+      </c>
+      <c r="K66" t="str">
+        <v>big-image</v>
+      </c>
+    </row>
+    <row r="67" xml:space="preserve">
+      <c r="A67" t="str">
+        <v>text</v>
+      </c>
+      <c r="B67" t="str">
+        <v>r4_ws_word3</v>
+      </c>
+      <c r="C67" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Discovered Word 3: (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D67" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E67" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F67" t="str">
+        <v>❌ Word 3 is mandatory.</v>
+      </c>
+      <c r="J67" t="str">
+        <v>aiml.jpeg</v>
+      </c>
+      <c r="K67" t="str">
+        <v>big-image</v>
+      </c>
+    </row>
+    <row r="68" xml:space="preserve">
+      <c r="A68" t="str">
+        <v>text</v>
+      </c>
+      <c r="B68" t="str">
+        <v>r4_ws_word4</v>
+      </c>
+      <c r="C68" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Discovered Word 4: (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D68" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E68" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F68" t="str">
+        <v>❌ Word 4 is mandatory.</v>
+      </c>
+      <c r="J68" t="str">
+        <v>aiml.jpeg</v>
+      </c>
+      <c r="K68" t="str">
+        <v>big-image</v>
+      </c>
+    </row>
+    <row r="69" xml:space="preserve">
+      <c r="A69" t="str">
+        <v>text</v>
+      </c>
+      <c r="B69" t="str">
+        <v>r4_ws_word5</v>
+      </c>
+      <c r="C69" t="str" xml:space="preserve">
+        <v xml:space="preserve">Enter Discovered Word 5: (MANDATORY)
+Enter code in caps</v>
+      </c>
+      <c r="D69" t="str">
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
+      </c>
+      <c r="E69" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F69" t="str">
+        <v>❌ Word 5 is mandatory.</v>
+      </c>
+      <c r="J69" t="str">
+        <v>aiml.jpeg</v>
+      </c>
+      <c r="K69" t="str">
+        <v>big-image</v>
+      </c>
+    </row>
+    <row r="70" xml:space="preserve">
+      <c r="A70" t="str">
         <v>note</v>
       </c>
-      <c r="B65" t="str">
-        <v>r4_wordsearch_intro</v>
-      </c>
-      <c r="C65" t="str" xml:space="preserve">
-        <v xml:space="preserve">Examine the puzzle image below.
-Find and enter ANY 5 words from the grid amongst:
+      <c r="B70" t="str">
+        <v>r4_wordsearch_reveal_note</v>
+      </c>
+      <c r="C70" t="str" xml:space="preserve">
+        <v xml:space="preserve">🧩 WORDS FOUND IN THE PUZZLE:
+Here are the words hidden in the puzzle:
 • MACHINE LEARNING
 • NEURAL NETWORK
 • PYTHON
@@ -1834,163 +1986,14 @@
 • MODELING
 • REGRESSION
 • CLASSIFY
-Enter code in caps</v>
-      </c>
-      <c r="D65" t="str">
-        <v>Find 5 words in the image and enter below in CAPS.</v>
-      </c>
-      <c r="J65" t="str">
-        <v>aiml.jpeg</v>
-      </c>
-    </row>
-    <row r="66" xml:space="preserve">
-      <c r="A66" t="str">
-        <v>text</v>
-      </c>
-      <c r="B66" t="str">
-        <v>r4_ws_word1</v>
-      </c>
-      <c r="C66" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Discovered Word 1: (MANDATORY)
-Enter code in caps</v>
-      </c>
-      <c r="D66" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E66" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F66" t="str">
-        <v>❌ Word 1 is mandatory.</v>
-      </c>
-      <c r="G66" t="str">
-        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'MACHINE LEARNING' or normalize-space(.) = 'NEURAL NETWORK' or normalize-space(.) = 'PYTHON' or normalize-space(.) = 'DATASET' or normalize-space(.) = 'ALGORITHM' or normalize-space(.) = 'TRAINING DATA' or normalize-space(.) = 'DEEP LEARNING' or normalize-space(.) = 'DATA MINING' or normalize-space(.) = 'MODELING' or normalize-space(.) = 'REGRESSION' or normalize-space(.) = 'CLASSIFY')</v>
-      </c>
-      <c r="H66" t="str">
-        <v>❌ Invalid word. Enter a valid word found in the puzzle in UPPERCASE (CAPS ONLY).</v>
-      </c>
-      <c r="J66" t="str">
-        <v>aiml.jpeg</v>
-      </c>
-    </row>
-    <row r="67" xml:space="preserve">
-      <c r="A67" t="str">
-        <v>text</v>
-      </c>
-      <c r="B67" t="str">
-        <v>r4_ws_word2</v>
-      </c>
-      <c r="C67" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Discovered Word 2: (MANDATORY)
-Enter code in caps</v>
-      </c>
-      <c r="D67" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E67" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F67" t="str">
-        <v>❌ Word 2 is mandatory.</v>
-      </c>
-      <c r="G67" t="str">
-        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'MACHINE LEARNING' or normalize-space(.) = 'NEURAL NETWORK' or normalize-space(.) = 'PYTHON' or normalize-space(.) = 'DATASET' or normalize-space(.) = 'ALGORITHM' or normalize-space(.) = 'TRAINING DATA' or normalize-space(.) = 'DEEP LEARNING' or normalize-space(.) = 'DATA MINING' or normalize-space(.) = 'MODELING' or normalize-space(.) = 'REGRESSION' or normalize-space(.) = 'CLASSIFY') and normalize-space(.) != normalize-space(${r4_ws_word1})</v>
-      </c>
-      <c r="H67" t="str">
-        <v>❌ Invalid or duplicate word. Enter a different valid word from the puzzle in UPPERCASE (CAPS ONLY).</v>
-      </c>
-      <c r="J67" t="str">
-        <v>aiml.jpeg</v>
-      </c>
-    </row>
-    <row r="68" xml:space="preserve">
-      <c r="A68" t="str">
-        <v>text</v>
-      </c>
-      <c r="B68" t="str">
-        <v>r4_ws_word3</v>
-      </c>
-      <c r="C68" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Discovered Word 3: (MANDATORY)
-Enter code in caps</v>
-      </c>
-      <c r="D68" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E68" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F68" t="str">
-        <v>❌ Word 3 is mandatory.</v>
-      </c>
-      <c r="G68" t="str">
-        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'MACHINE LEARNING' or normalize-space(.) = 'NEURAL NETWORK' or normalize-space(.) = 'PYTHON' or normalize-space(.) = 'DATASET' or normalize-space(.) = 'ALGORITHM' or normalize-space(.) = 'TRAINING DATA' or normalize-space(.) = 'DEEP LEARNING' or normalize-space(.) = 'DATA MINING' or normalize-space(.) = 'MODELING' or normalize-space(.) = 'REGRESSION' or normalize-space(.) = 'CLASSIFY') and normalize-space(.) != normalize-space(${r4_ws_word1}) and normalize-space(.) != normalize-space(${r4_ws_word2})</v>
-      </c>
-      <c r="H68" t="str">
-        <v>❌ Invalid or duplicate word. Enter a different valid word from the puzzle in UPPERCASE (CAPS ONLY).</v>
-      </c>
-      <c r="J68" t="str">
-        <v>aiml.jpeg</v>
-      </c>
-    </row>
-    <row r="69" xml:space="preserve">
-      <c r="A69" t="str">
-        <v>text</v>
-      </c>
-      <c r="B69" t="str">
-        <v>r4_ws_word4</v>
-      </c>
-      <c r="C69" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Discovered Word 4: (MANDATORY)
-Enter code in caps</v>
-      </c>
-      <c r="D69" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E69" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F69" t="str">
-        <v>❌ Word 4 is mandatory.</v>
-      </c>
-      <c r="G69" t="str">
-        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'MACHINE LEARNING' or normalize-space(.) = 'NEURAL NETWORK' or normalize-space(.) = 'PYTHON' or normalize-space(.) = 'DATASET' or normalize-space(.) = 'ALGORITHM' or normalize-space(.) = 'TRAINING DATA' or normalize-space(.) = 'DEEP LEARNING' or normalize-space(.) = 'DATA MINING' or normalize-space(.) = 'MODELING' or normalize-space(.) = 'REGRESSION' or normalize-space(.) = 'CLASSIFY') and normalize-space(.) != normalize-space(${r4_ws_word1}) and normalize-space(.) != normalize-space(${r4_ws_word2}) and normalize-space(.) != normalize-space(${r4_ws_word3})</v>
-      </c>
-      <c r="H69" t="str">
-        <v>❌ Invalid or duplicate word. Enter a different valid word from the puzzle in UPPERCASE (CAPS ONLY).</v>
-      </c>
-      <c r="J69" t="str">
-        <v>aiml.jpeg</v>
-      </c>
-    </row>
-    <row r="70" xml:space="preserve">
-      <c r="A70" t="str">
-        <v>text</v>
-      </c>
-      <c r="B70" t="str">
-        <v>r4_ws_word5</v>
-      </c>
-      <c r="C70" t="str" xml:space="preserve">
-        <v xml:space="preserve">Enter Discovered Word 5: (MANDATORY)
+Study these concepts and decode which campus block/department they relate to!
 Enter code in caps</v>
       </c>
       <c r="D70" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
-      </c>
-      <c r="E70" t="str">
-        <v>yes</v>
-      </c>
-      <c r="F70" t="str">
-        <v>❌ Word 5 is mandatory.</v>
-      </c>
-      <c r="G70" t="str">
-        <v>regex(., '^[A-Z ]+$') and (normalize-space(.) = 'MACHINE LEARNING' or normalize-space(.) = 'NEURAL NETWORK' or normalize-space(.) = 'PYTHON' or normalize-space(.) = 'DATASET' or normalize-space(.) = 'ALGORITHM' or normalize-space(.) = 'TRAINING DATA' or normalize-space(.) = 'DEEP LEARNING' or normalize-space(.) = 'DATA MINING' or normalize-space(.) = 'MODELING' or normalize-space(.) = 'REGRESSION' or normalize-space(.) = 'CLASSIFY') and normalize-space(.) != normalize-space(${r4_ws_word1}) and normalize-space(.) != normalize-space(${r4_ws_word2}) and normalize-space(.) != normalize-space(${r4_ws_word3}) and normalize-space(.) != normalize-space(${r4_ws_word4})</v>
-      </c>
-      <c r="H70" t="str">
-        <v>❌ Invalid or duplicate word. Enter a different valid word from the puzzle in UPPERCASE (CAPS ONLY).</v>
-      </c>
-      <c r="J70" t="str">
-        <v>aiml.jpeg</v>
+        <v>Decode the related department/block based on these words.</v>
+      </c>
+      <c r="I70" t="str">
+        <v>${r4_ws_word1} != '' and ${r4_ws_word2} != '' and ${r4_ws_word3} != '' and ${r4_ws_word4} != '' and ${r4_ws_word5} != ''</v>
       </c>
     </row>
     <row r="71" xml:space="preserve">
@@ -2001,11 +2004,11 @@
         <v>r4_aiml_destination</v>
       </c>
       <c r="C71" t="str" xml:space="preserve">
-        <v xml:space="preserve">Deduce the location related to these words: (MANDATORY)
+        <v xml:space="preserve">Decode the related block/location: (MANDATORY)
 Enter code in caps</v>
       </c>
       <c r="D71" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E71" t="str">
         <v>yes</v>
@@ -2020,10 +2023,13 @@
         <v>❌ Incorrect destination. Enter the location in UPPERCASE (CAPS ONLY).</v>
       </c>
       <c r="I71" t="str">
-        <v>(normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY')</v>
+        <v>${r4_ws_word1} != '' and ${r4_ws_word2} != '' and ${r4_ws_word3} != '' and ${r4_ws_word4} != '' and ${r4_ws_word5} != ''</v>
       </c>
       <c r="J71" t="str">
         <v>aiml.jpeg</v>
+      </c>
+      <c r="K71" t="str">
+        <v>big-image</v>
       </c>
     </row>
     <row r="72" xml:space="preserve">
@@ -2041,7 +2047,7 @@
         <v>Go to the location and ask volunteer for start code.</v>
       </c>
       <c r="I72" t="str">
-        <v>(normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML')</v>
+        <v>${r4_ws_word1} != '' and ${r4_ws_word2} != '' and ${r4_ws_word3} != '' and ${r4_ws_word4} != '' and ${r4_ws_word5} != '' and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML')</v>
       </c>
     </row>
     <row r="73" xml:space="preserve">
@@ -2056,7 +2062,7 @@
 Enter code in caps</v>
       </c>
       <c r="D73" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E73" t="str">
         <v>yes</v>
@@ -2071,7 +2077,7 @@
         <v>❌ Incorrect START CODE. Enter the code in UPPERCASE (CAPS ONLY) provided by the volunteer.</v>
       </c>
       <c r="I73" t="str">
-        <v>(normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML')</v>
+        <v>${r4_ws_word1} != '' and ${r4_ws_word2} != '' and ${r4_ws_word3} != '' and ${r4_ws_word4} != '' and ${r4_ws_word5} != '' and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML')</v>
       </c>
     </row>
     <row r="74">
@@ -2090,7 +2096,7 @@
         <v>ROUND 4 — PHYSICAL CHALLENGE</v>
       </c>
       <c r="I75" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and (normalize-space(${r3_lib_volunteer_code}) = 'DUMB_FAKE' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-HUNT-GOOD' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-PASS' or normalize-space(${r3_lib_volunteer_code}) = 'QR-LIB-2') and (normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY')</v>
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and (normalize-space(${r2_var_a_code}) = 'MBA-QF-1' or normalize-space(${r2_var_a_code}) = 'MB-QF-1' or normalize-space(${r2_var_a_code}) = 'MBA_QF_1')) or (${mba_variant_select} = 'var_b' and (normalize-space(${r2_var_b_code}) = 'MBA-BQ-2' or normalize-space(${r2_var_b_code}) = 'MB-BQ-2' or normalize-space(${r2_var_b_code}) = 'MBA_BQ_2' or normalize-space(${r2_var_b_code}) = 'MB_BQ_2'))) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and ${r4_ws_word1} != '' and ${r4_ws_word2} != '' and ${r4_ws_word3} != '' and ${r4_ws_word4} != '' and ${r4_ws_word5} != '' and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY')</v>
       </c>
     </row>
     <row r="76" xml:space="preserve">
@@ -2143,7 +2149,7 @@
 Enter code in caps</v>
       </c>
       <c r="D78" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E78" t="str">
         <v>yes</v>
@@ -2174,7 +2180,7 @@
         <v>FINAL ROUND</v>
       </c>
       <c r="I80" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and (normalize-space(${r3_lib_volunteer_code}) = 'DUMB_FAKE' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-HUNT-GOOD' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-PASS' or normalize-space(${r3_lib_volunteer_code}) = 'QR-LIB-2') and (normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != ''</v>
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and (normalize-space(${r2_var_a_code}) = 'MBA-QF-1' or normalize-space(${r2_var_a_code}) = 'MB-QF-1' or normalize-space(${r2_var_a_code}) = 'MBA_QF_1')) or (${mba_variant_select} = 'var_b' and (normalize-space(${r2_var_b_code}) = 'MBA-BQ-2' or normalize-space(${r2_var_b_code}) = 'MB-BQ-2' or normalize-space(${r2_var_b_code}) = 'MBA_BQ_2' or normalize-space(${r2_var_b_code}) = 'MB_BQ_2'))) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and ${r4_ws_word1} != '' and ${r4_ws_word2} != '' and ${r4_ws_word3} != '' and ${r4_ws_word4} != '' and ${r4_ws_word5} != '' and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != ''</v>
       </c>
     </row>
     <row r="81" xml:space="preserve">
@@ -2211,7 +2217,7 @@
 Enter code in caps</v>
       </c>
       <c r="D82" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E82" t="str">
         <v>yes</v>
@@ -2241,7 +2247,7 @@
 Enter code in caps</v>
       </c>
       <c r="D83" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E83" t="str">
         <v>yes</v>
@@ -2256,7 +2262,7 @@
         <v>❌ Incorrect answer. Solve Riddle 2 and enter in UPPERCASE (CAPS ONLY).</v>
       </c>
       <c r="I83" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and (normalize-space(${r3_lib_volunteer_code}) = 'DUMB_FAKE' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-HUNT-GOOD' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-PASS' or normalize-space(${r3_lib_volunteer_code}) = 'QR-LIB-2') and (normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI')</v>
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and (normalize-space(${r2_var_a_code}) = 'MBA-QF-1' or normalize-space(${r2_var_a_code}) = 'MB-QF-1' or normalize-space(${r2_var_a_code}) = 'MBA_QF_1')) or (${mba_variant_select} = 'var_b' and (normalize-space(${r2_var_b_code}) = 'MBA-BQ-2' or normalize-space(${r2_var_b_code}) = 'MB-BQ-2' or normalize-space(${r2_var_b_code}) = 'MBA_BQ_2' or normalize-space(${r2_var_b_code}) = 'MB_BQ_2'))) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and ${r4_ws_word1} != '' and ${r4_ws_word2} != '' and ${r4_ws_word3} != '' and ${r4_ws_word4} != '' and ${r4_ws_word5} != '' and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI')</v>
       </c>
     </row>
     <row r="84" xml:space="preserve">
@@ -2275,7 +2281,7 @@
         <v>Go to the stage to solve the final puzzle.</v>
       </c>
       <c r="I84" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and (normalize-space(${r3_lib_volunteer_code}) = 'DUMB_FAKE' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-HUNT-GOOD' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-PASS' or normalize-space(${r3_lib_volunteer_code}) = 'QR-LIB-2') and (normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and (normalize-space(${r2_var_a_code}) = 'MBA-QF-1' or normalize-space(${r2_var_a_code}) = 'MB-QF-1' or normalize-space(${r2_var_a_code}) = 'MBA_QF_1')) or (${mba_variant_select} = 'var_b' and (normalize-space(${r2_var_b_code}) = 'MBA-BQ-2' or normalize-space(${r2_var_b_code}) = 'MB-BQ-2' or normalize-space(${r2_var_b_code}) = 'MBA_BQ_2' or normalize-space(${r2_var_b_code}) = 'MB_BQ_2'))) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and ${r4_ws_word1} != '' and ${r4_ws_word2} != '' and ${r4_ws_word3} != '' and ${r4_ws_word4} != '' and ${r4_ws_word5} != '' and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
       </c>
     </row>
     <row r="85" xml:space="preserve">
@@ -2299,7 +2305,7 @@
         <v>❌ Photo of the solved puzzle is mandatory.</v>
       </c>
       <c r="I85" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and (normalize-space(${r3_lib_volunteer_code}) = 'DUMB_FAKE' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-HUNT-GOOD' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-PASS' or normalize-space(${r3_lib_volunteer_code}) = 'QR-LIB-2') and (normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and (normalize-space(${r2_var_a_code}) = 'MBA-QF-1' or normalize-space(${r2_var_a_code}) = 'MB-QF-1' or normalize-space(${r2_var_a_code}) = 'MBA_QF_1')) or (${mba_variant_select} = 'var_b' and (normalize-space(${r2_var_b_code}) = 'MBA-BQ-2' or normalize-space(${r2_var_b_code}) = 'MB-BQ-2' or normalize-space(${r2_var_b_code}) = 'MBA_BQ_2' or normalize-space(${r2_var_b_code}) = 'MB_BQ_2'))) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and ${r4_ws_word1} != '' and ${r4_ws_word2} != '' and ${r4_ws_word3} != '' and ${r4_ws_word4} != '' and ${r4_ws_word5} != '' and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
       </c>
     </row>
     <row r="86" xml:space="preserve">
@@ -2314,7 +2320,7 @@
 Enter code in caps</v>
       </c>
       <c r="D86" t="str">
-        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY.</v>
+        <v>ENTER CODE/ANSWER IN CAPITAL LETTERS ONLY. Read the question properly as you cannot come back to the question once you go ahead.</v>
       </c>
       <c r="E86" t="str">
         <v>yes</v>
@@ -2329,7 +2335,7 @@
         <v>❌ Incorrect code. Enter the code in UPPERCASE (CAPS ONLY) provided by the Chief Judge.</v>
       </c>
       <c r="I86" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and (normalize-space(${r3_lib_volunteer_code}) = 'DUMB_FAKE' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-HUNT-GOOD' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-PASS' or normalize-space(${r3_lib_volunteer_code}) = 'QR-LIB-2') and (normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and (normalize-space(${r2_var_a_code}) = 'MBA-QF-1' or normalize-space(${r2_var_a_code}) = 'MB-QF-1' or normalize-space(${r2_var_a_code}) = 'MBA_QF_1')) or (${mba_variant_select} = 'var_b' and (normalize-space(${r2_var_b_code}) = 'MBA-BQ-2' or normalize-space(${r2_var_b_code}) = 'MB-BQ-2' or normalize-space(${r2_var_b_code}) = 'MBA_BQ_2' or normalize-space(${r2_var_b_code}) = 'MB_BQ_2'))) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and ${r4_ws_word1} != '' and ${r4_ws_word2} != '' and ${r4_ws_word3} != '' and ${r4_ws_word4} != '' and ${r4_ws_word5} != '' and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE'</v>
       </c>
     </row>
     <row r="87" xml:space="preserve">
@@ -2348,7 +2354,7 @@
         <v>Run to ring the bell to claim victory!</v>
       </c>
       <c r="I87" t="str">
-        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and normalize-space(${r2_var_a_code}) = 'MBA-QF-1') or (${mba_variant_select} = 'var_b' and normalize-space(${r2_var_b_code}) = 'MB-BQ-2')) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and (normalize-space(${r3_lib_volunteer_code}) = 'DUMB_FAKE' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-HUNT-GOOD' or normalize-space(${r3_lib_volunteer_code}) = 'LIB-PASS' or normalize-space(${r3_lib_volunteer_code}) = 'QR-LIB-2') and (normalize-space(${r4_ws_word1}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word1}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word1}) = 'PYTHON' or normalize-space(${r4_ws_word1}) = 'DATASET' or normalize-space(${r4_ws_word1}) = 'ALGORITHM' or normalize-space(${r4_ws_word1}) = 'TRAINING DATA' or normalize-space(${r4_ws_word1}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word1}) = 'DATA MINING' or normalize-space(${r4_ws_word1}) = 'MODELING' or normalize-space(${r4_ws_word1}) = 'REGRESSION' or normalize-space(${r4_ws_word1}) = 'CLASSIFY') and (normalize-space(${r4_ws_word2}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word2}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word2}) = 'PYTHON' or normalize-space(${r4_ws_word2}) = 'DATASET' or normalize-space(${r4_ws_word2}) = 'ALGORITHM' or normalize-space(${r4_ws_word2}) = 'TRAINING DATA' or normalize-space(${r4_ws_word2}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word2}) = 'DATA MINING' or normalize-space(${r4_ws_word2}) = 'MODELING' or normalize-space(${r4_ws_word2}) = 'REGRESSION' or normalize-space(${r4_ws_word2}) = 'CLASSIFY') and (normalize-space(${r4_ws_word3}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word3}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word3}) = 'PYTHON' or normalize-space(${r4_ws_word3}) = 'DATASET' or normalize-space(${r4_ws_word3}) = 'ALGORITHM' or normalize-space(${r4_ws_word3}) = 'TRAINING DATA' or normalize-space(${r4_ws_word3}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word3}) = 'DATA MINING' or normalize-space(${r4_ws_word3}) = 'MODELING' or normalize-space(${r4_ws_word3}) = 'REGRESSION' or normalize-space(${r4_ws_word3}) = 'CLASSIFY') and (normalize-space(${r4_ws_word4}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word4}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word4}) = 'PYTHON' or normalize-space(${r4_ws_word4}) = 'DATASET' or normalize-space(${r4_ws_word4}) = 'ALGORITHM' or normalize-space(${r4_ws_word4}) = 'TRAINING DATA' or normalize-space(${r4_ws_word4}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word4}) = 'DATA MINING' or normalize-space(${r4_ws_word4}) = 'MODELING' or normalize-space(${r4_ws_word4}) = 'REGRESSION' or normalize-space(${r4_ws_word4}) = 'CLASSIFY') and (normalize-space(${r4_ws_word5}) = 'MACHINE LEARNING' or normalize-space(${r4_ws_word5}) = 'NEURAL NETWORK' or normalize-space(${r4_ws_word5}) = 'PYTHON' or normalize-space(${r4_ws_word5}) = 'DATASET' or normalize-space(${r4_ws_word5}) = 'ALGORITHM' or normalize-space(${r4_ws_word5}) = 'TRAINING DATA' or normalize-space(${r4_ws_word5}) = 'DEEP LEARNING' or normalize-space(${r4_ws_word5}) = 'DATA MINING' or normalize-space(${r4_ws_word5}) = 'MODELING' or normalize-space(${r4_ws_word5}) = 'REGRESSION' or normalize-space(${r4_ws_word5}) = 'CLASSIFY') and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE' and (normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH2' or normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH1') and ${final_solved_puzzle_photo} != ''</v>
+        <v>${team_name} != '' and ${player_id} != '' and ${team_start_photo} != '' and normalize-space(${r1_admin_code}) = 'JOHN-CENA' and ${r1_admin_photo} != '' and (normalize-space(${r2_mba_loc_answer}) = 'MBA' or normalize-space(${r2_mba_loc_answer}) = 'MBA BLOCK') and normalize-space(${r2_start_code}) = 'MBA-START' and ((${mba_variant_select} = 'var_a' and (normalize-space(${r2_var_a_code}) = 'MBA-QF-1' or normalize-space(${r2_var_a_code}) = 'MB-QF-1' or normalize-space(${r2_var_a_code}) = 'MBA_QF_1')) or (${mba_variant_select} = 'var_b' and (normalize-space(${r2_var_b_code}) = 'MBA-BQ-2' or normalize-space(${r2_var_b_code}) = 'MB-BQ-2' or normalize-space(${r2_var_b_code}) = 'MBA_BQ_2' or normalize-space(${r2_var_b_code}) = 'MB_BQ_2'))) and (normalize-space(${r3_decode_w1}) = 'SHELVES' and normalize-space(${r3_decode_w2}) = 'READING' and normalize-space(${r3_decode_w3}) = 'WIFI' and normalize-space(${r3_decode_w4}) = 'DISCUSSION LOUNGE' and normalize-space(${r3_decode_w5}) = 'DIGITAL LIBRARY') and (normalize-space(${r3_lib_loc_answer}) = 'LIBRARY' or normalize-space(${r3_lib_loc_answer}) = 'CENTRAL LIBRARY') and normalize-space(${r3_lib_qr_scan}) = 'DUMB_FAKE' and ${r4_ws_word1} != '' and ${r4_ws_word2} != '' and ${r4_ws_word3} != '' and ${r4_ws_word4} != '' and ${r4_ws_word5} != '' and (normalize-space(${r4_aiml_destination}) = 'AIML' or normalize-space(${r4_aiml_destination}) = 'AI ML' or normalize-space(${r4_aiml_destination}) = 'AIML BLOCK' or normalize-space(${r4_aiml_destination}) = 'AI/ML' or normalize-space(${r4_aiml_destination}) = 'AI &amp; ML') and (normalize-space(${r4_start_code}) = 'START-AI-PHY' or normalize-space(${r4_start_code}) = 'START-PHY') and (normalize-space(${r4_phy_code}) = 'PHY-AIML' or normalize-space(${r4_phy_code}) = 'PHY-CY') and ${r4_phy_photo} != '' and (normalize-space(${final_riddle1_answer}) = 'AUDITORIUM' or normalize-space(${final_riddle1_answer}) = 'AUDI') and normalize-space(${final_riddle2_stage_answer}) = 'STAGE' and (normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH2' or normalize-space(${final_stage_volunteer_code}) = 'FINAL-PATH1') and ${final_solved_puzzle_photo} != ''</v>
       </c>
     </row>
     <row r="88">
@@ -2358,7 +2364,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J88"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K88"/>
   </ignoredErrors>
 </worksheet>
 </file>
